--- a/data/project/dictionary/data_dictionary.xlsx
+++ b/data/project/dictionary/data_dictionary.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dictionary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dimensions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Facts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dictionary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dimensions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grain" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,33 +428,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E163"/>
+  <dimension ref="A1:K163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TableName</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TableType</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>TableDescription</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ColumnName</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ExampleValues</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>KPIUsage</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>DataQualityNotes</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Relationships</t>
         </is>
       </c>
     </row>
@@ -458,17 +501,47 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Calendario para inteligencia de tiempo en operaciones mineras, mantenimiento, energia, seguridad y proyectos.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Una fila por día calendario.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>DateKey</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>DateKey de Dim_Fecha. Calendario para inteligencia de tiempo.</t>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Clave de fecha en formato yyyymmdd. Permite relacionar hechos con Dim_Fecha sin depender de formatos regionales.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Debe ser único si es PK y consistente si se usa como FK.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Fact_Proyectos.DateKey -&gt; DateKey; Fact_OrdenesTrabajo.CreatedDateKey -&gt; DateKey; Fact_Costos.DateKey -&gt; DateKey; Fact_SLA.CreatedDateKey -&gt; DateKey; Fact_Mantenimiento.DateKey -&gt; DateKey; Fact_Incidentes.DateKey -&gt; DateKey; Fact_Energia.DateKey -&gt; DateKey; Fact_Productividad.DateKey -&gt; DateKey</t>
         </is>
       </c>
     </row>
@@ -485,17 +558,47 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Calendario para inteligencia de tiempo en operaciones mineras, mantenimiento, energia, seguridad y proyectos.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Una fila por día calendario.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Date de Dim_Fecha. Calendario para inteligencia de tiempo.</t>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fecha calendario legible. Se usa para filtros, ejes temporales y validación de rangos.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Fact_Proyectos.DateKey -&gt; DateKey; Fact_OrdenesTrabajo.CreatedDateKey -&gt; DateKey; Fact_Costos.DateKey -&gt; DateKey; Fact_SLA.CreatedDateKey -&gt; DateKey; Fact_Mantenimiento.DateKey -&gt; DateKey; Fact_Incidentes.DateKey -&gt; DateKey; Fact_Energia.DateKey -&gt; DateKey; Fact_Productividad.DateKey -&gt; DateKey</t>
         </is>
       </c>
     </row>
@@ -512,17 +615,47 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Calendario para inteligencia de tiempo en operaciones mineras, mantenimiento, energia, seguridad y proyectos.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Una fila por día calendario.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Year de Dim_Fecha. Calendario para inteligencia de tiempo.</t>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Año calendario.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Fact_Proyectos.DateKey -&gt; DateKey; Fact_OrdenesTrabajo.CreatedDateKey -&gt; DateKey; Fact_Costos.DateKey -&gt; DateKey; Fact_SLA.CreatedDateKey -&gt; DateKey; Fact_Mantenimiento.DateKey -&gt; DateKey; Fact_Incidentes.DateKey -&gt; DateKey; Fact_Energia.DateKey -&gt; DateKey; Fact_Productividad.DateKey -&gt; DateKey</t>
         </is>
       </c>
     </row>
@@ -539,17 +672,47 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Calendario para inteligencia de tiempo en operaciones mineras, mantenimiento, energia, seguridad y proyectos.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Una fila por día calendario.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Quarter</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Quarter de Dim_Fecha. Calendario para inteligencia de tiempo.</t>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Trimestre calendario.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Fact_Proyectos.DateKey -&gt; DateKey; Fact_OrdenesTrabajo.CreatedDateKey -&gt; DateKey; Fact_Costos.DateKey -&gt; DateKey; Fact_SLA.CreatedDateKey -&gt; DateKey; Fact_Mantenimiento.DateKey -&gt; DateKey; Fact_Incidentes.DateKey -&gt; DateKey; Fact_Energia.DateKey -&gt; DateKey; Fact_Productividad.DateKey -&gt; DateKey</t>
         </is>
       </c>
     </row>
@@ -566,17 +729,47 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Calendario para inteligencia de tiempo en operaciones mineras, mantenimiento, energia, seguridad y proyectos.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Una fila por día calendario.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>MonthNumber</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>MonthNumber de Dim_Fecha. Calendario para inteligencia de tiempo.</t>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Número de mes entre 1 y 12.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Fact_Proyectos.DateKey -&gt; DateKey; Fact_OrdenesTrabajo.CreatedDateKey -&gt; DateKey; Fact_Costos.DateKey -&gt; DateKey; Fact_SLA.CreatedDateKey -&gt; DateKey; Fact_Mantenimiento.DateKey -&gt; DateKey; Fact_Incidentes.DateKey -&gt; DateKey; Fact_Energia.DateKey -&gt; DateKey; Fact_Productividad.DateKey -&gt; DateKey</t>
         </is>
       </c>
     </row>
@@ -593,17 +786,47 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Calendario para inteligencia de tiempo en operaciones mineras, mantenimiento, energia, seguridad y proyectos.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Una fila por día calendario.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>MonthName</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MonthName de Dim_Fecha. Calendario para inteligencia de tiempo.</t>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nombre del mes en español.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Fact_Proyectos.DateKey -&gt; DateKey; Fact_OrdenesTrabajo.CreatedDateKey -&gt; DateKey; Fact_Costos.DateKey -&gt; DateKey; Fact_SLA.CreatedDateKey -&gt; DateKey; Fact_Mantenimiento.DateKey -&gt; DateKey; Fact_Incidentes.DateKey -&gt; DateKey; Fact_Energia.DateKey -&gt; DateKey; Fact_Productividad.DateKey -&gt; DateKey</t>
         </is>
       </c>
     </row>
@@ -620,17 +843,47 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Calendario para inteligencia de tiempo en operaciones mineras, mantenimiento, energia, seguridad y proyectos.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Una fila por día calendario.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>WeekNumber</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>WeekNumber de Dim_Fecha. Calendario para inteligencia de tiempo.</t>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Número de semana ISO aproximado para análisis semanal.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Fact_Proyectos.DateKey -&gt; DateKey; Fact_OrdenesTrabajo.CreatedDateKey -&gt; DateKey; Fact_Costos.DateKey -&gt; DateKey; Fact_SLA.CreatedDateKey -&gt; DateKey; Fact_Mantenimiento.DateKey -&gt; DateKey; Fact_Incidentes.DateKey -&gt; DateKey; Fact_Energia.DateKey -&gt; DateKey; Fact_Productividad.DateKey -&gt; DateKey</t>
         </is>
       </c>
     </row>
@@ -647,17 +900,47 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Calendario para inteligencia de tiempo en operaciones mineras, mantenimiento, energia, seguridad y proyectos.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Una fila por día calendario.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>DayOfWeek</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>DayOfWeek de Dim_Fecha. Calendario para inteligencia de tiempo.</t>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Día de la semana en español.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Fact_Proyectos.DateKey -&gt; DateKey; Fact_OrdenesTrabajo.CreatedDateKey -&gt; DateKey; Fact_Costos.DateKey -&gt; DateKey; Fact_SLA.CreatedDateKey -&gt; DateKey; Fact_Mantenimiento.DateKey -&gt; DateKey; Fact_Incidentes.DateKey -&gt; DateKey; Fact_Energia.DateKey -&gt; DateKey; Fact_Productividad.DateKey -&gt; DateKey</t>
         </is>
       </c>
     </row>
@@ -674,17 +957,47 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Calendario para inteligencia de tiempo en operaciones mineras, mantenimiento, energia, seguridad y proyectos.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Una fila por día calendario.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>IsWeekend</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>IsWeekend de Dim_Fecha. Calendario para inteligencia de tiempo.</t>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Indica si la fecha cae en fin de semana.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Fact_Proyectos.DateKey -&gt; DateKey; Fact_OrdenesTrabajo.CreatedDateKey -&gt; DateKey; Fact_Costos.DateKey -&gt; DateKey; Fact_SLA.CreatedDateKey -&gt; DateKey; Fact_Mantenimiento.DateKey -&gt; DateKey; Fact_Incidentes.DateKey -&gt; DateKey; Fact_Energia.DateKey -&gt; DateKey; Fact_Productividad.DateKey -&gt; DateKey</t>
         </is>
       </c>
     </row>
@@ -701,17 +1014,47 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>Areas sinteticas de una operacion minera Tech&amp;Eng: mina, planta concentradora, relaves, mantenimiento, energia, HSE y OT.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Una fila por área o proceso minero sintético.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>AreaID</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AreaID de Dim_Area. Áreas operativas y unidades de negocio.</t>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Clave del área minera. En dimensiones es identificador; en hechos es llave foránea hacia Dim_Area.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Debe ser único si es PK y consistente si se usa como FK.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Dim_Equipo.AreaID -&gt; AreaID; LocationID -&gt; Dim_Ubicacion.LocationID; Dim_Proyecto.AreaID -&gt; AreaID; Fact_Proyectos.AreaID -&gt; AreaID; Fact_OrdenesTrabajo.AreaID -&gt; AreaID; Fact_SLA.AreaID -&gt; AreaID; Fact_Mantenimiento.AreaID -&gt; AreaID; Fact_Incidentes.AreaID -&gt; AreaID; Fact_Energia.AreaID -&gt; AreaID; Fact_Productividad.AreaID -&gt; AreaID</t>
         </is>
       </c>
     </row>
@@ -728,17 +1071,47 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>Areas sinteticas de una operacion minera Tech&amp;Eng: mina, planta concentradora, relaves, mantenimiento, energia, HSE y OT.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Una fila por área o proceso minero sintético.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>AreaName</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AreaName de Dim_Area. Áreas operativas y unidades de negocio.</t>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nombre del proceso o área minera sintética, por ejemplo Chancado Primario, Molienda o Taller Mina.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Chancado Primario; Molienda; Espesamiento y Relaves</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Dim_Equipo.AreaID -&gt; AreaID; LocationID -&gt; Dim_Ubicacion.LocationID; Dim_Proyecto.AreaID -&gt; AreaID; Fact_Proyectos.AreaID -&gt; AreaID; Fact_OrdenesTrabajo.AreaID -&gt; AreaID; Fact_SLA.AreaID -&gt; AreaID; Fact_Mantenimiento.AreaID -&gt; AreaID; Fact_Incidentes.AreaID -&gt; AreaID; Fact_Energia.AreaID -&gt; AreaID; Fact_Productividad.AreaID -&gt; AreaID</t>
         </is>
       </c>
     </row>
@@ -755,17 +1128,47 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>Areas sinteticas de una operacion minera Tech&amp;Eng: mina, planta concentradora, relaves, mantenimiento, energia, HSE y OT.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Una fila por área o proceso minero sintético.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>BusinessUnit</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>BusinessUnit de Dim_Area. Áreas operativas y unidades de negocio.</t>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Unidad de negocio o superintendencia sintética a la que pertenece el área.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Dim_Equipo.AreaID -&gt; AreaID; LocationID -&gt; Dim_Ubicacion.LocationID; Dim_Proyecto.AreaID -&gt; AreaID; Fact_Proyectos.AreaID -&gt; AreaID; Fact_OrdenesTrabajo.AreaID -&gt; AreaID; Fact_SLA.AreaID -&gt; AreaID; Fact_Mantenimiento.AreaID -&gt; AreaID; Fact_Incidentes.AreaID -&gt; AreaID; Fact_Energia.AreaID -&gt; AreaID; Fact_Productividad.AreaID -&gt; AreaID</t>
         </is>
       </c>
     </row>
@@ -782,17 +1185,47 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>Areas sinteticas de una operacion minera Tech&amp;Eng: mina, planta concentradora, relaves, mantenimiento, energia, HSE y OT.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Una fila por área o proceso minero sintético.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>AreaType</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AreaType de Dim_Area. Áreas operativas y unidades de negocio.</t>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tipo analítico del área: Mina, Planta, Mantenimiento, Servicios, Seguridad, Ingeniería o Soporte Operacional.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Dim_Equipo.AreaID -&gt; AreaID; LocationID -&gt; Dim_Ubicacion.LocationID; Dim_Proyecto.AreaID -&gt; AreaID; Fact_Proyectos.AreaID -&gt; AreaID; Fact_OrdenesTrabajo.AreaID -&gt; AreaID; Fact_SLA.AreaID -&gt; AreaID; Fact_Mantenimiento.AreaID -&gt; AreaID; Fact_Incidentes.AreaID -&gt; AreaID; Fact_Energia.AreaID -&gt; AreaID; Fact_Productividad.AreaID -&gt; AreaID</t>
         </is>
       </c>
     </row>
@@ -809,17 +1242,47 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>Areas sinteticas de una operacion minera Tech&amp;Eng: mina, planta concentradora, relaves, mantenimiento, energia, HSE y OT.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Una fila por área o proceso minero sintético.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>ManagerName</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>ManagerName de Dim_Area. Áreas operativas y unidades de negocio.</t>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nombre sintético del responsable de gestión del área. No representa personas reales.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Dim_Equipo.AreaID -&gt; AreaID; LocationID -&gt; Dim_Ubicacion.LocationID; Dim_Proyecto.AreaID -&gt; AreaID; Fact_Proyectos.AreaID -&gt; AreaID; Fact_OrdenesTrabajo.AreaID -&gt; AreaID; Fact_SLA.AreaID -&gt; AreaID; Fact_Mantenimiento.AreaID -&gt; AreaID; Fact_Incidentes.AreaID -&gt; AreaID; Fact_Energia.AreaID -&gt; AreaID; Fact_Productividad.AreaID -&gt; AreaID</t>
         </is>
       </c>
     </row>
@@ -836,17 +1299,47 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>Areas sinteticas de una operacion minera Tech&amp;Eng: mina, planta concentradora, relaves, mantenimiento, energia, HSE y OT.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Una fila por área o proceso minero sintético.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>LocationID</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LocationID de Dim_Area. Áreas operativas y unidades de negocio.</t>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Clave de ubicación. En dimensiones es identificador; en hechos permite analizar por lugar físico de faena.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Debe ser único si es PK y consistente si se usa como FK.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Dim_Equipo.AreaID -&gt; AreaID; LocationID -&gt; Dim_Ubicacion.LocationID; Dim_Proyecto.AreaID -&gt; AreaID; Fact_Proyectos.AreaID -&gt; AreaID; Fact_OrdenesTrabajo.AreaID -&gt; AreaID; Fact_SLA.AreaID -&gt; AreaID; Fact_Mantenimiento.AreaID -&gt; AreaID; Fact_Incidentes.AreaID -&gt; AreaID; Fact_Energia.AreaID -&gt; AreaID; Fact_Productividad.AreaID -&gt; AreaID</t>
         </is>
       </c>
     </row>
@@ -863,17 +1356,47 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>Activos mineros e industriales sinteticos, con criticidad y pertenencia a areas operacionales.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Una fila por activo físico, equipo minero, equipo de planta o sistema OT.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>EquipmentID</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>EquipmentID de Dim_Equipo. Activos técnicos y criticidad.</t>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Clave del equipo o activo. En hechos permite conectar costos, mantenimiento, energía e incidentes con Dim_Equipo.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Debe ser único si es PK y consistente si se usa como FK.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; Fact_OrdenesTrabajo.EquipmentID -&gt; EquipmentID; Fact_Costos.EquipmentID -&gt; EquipmentID; Fact_Mantenimiento.EquipmentID -&gt; EquipmentID; Fact_Incidentes.EquipmentID -&gt; EquipmentID; Fact_Energia.EquipmentID -&gt; EquipmentID</t>
         </is>
       </c>
     </row>
@@ -890,17 +1413,47 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>Activos mineros e industriales sinteticos, con criticidad y pertenencia a areas operacionales.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Una fila por activo físico, equipo minero, equipo de planta o sistema OT.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>EquipmentName</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>EquipmentName de Dim_Equipo. Activos técnicos y criticidad.</t>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Nombre sintético del equipo, activo o sistema OT.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; Fact_OrdenesTrabajo.EquipmentID -&gt; EquipmentID; Fact_Costos.EquipmentID -&gt; EquipmentID; Fact_Mantenimiento.EquipmentID -&gt; EquipmentID; Fact_Incidentes.EquipmentID -&gt; EquipmentID; Fact_Energia.EquipmentID -&gt; EquipmentID</t>
         </is>
       </c>
     </row>
@@ -917,17 +1470,47 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>Activos mineros e industriales sinteticos, con criticidad y pertenencia a areas operacionales.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Una fila por activo físico, equipo minero, equipo de planta o sistema OT.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>EquipmentType</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>EquipmentType de Dim_Equipo. Activos técnicos y criticidad.</t>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tipo de equipo minero o industrial: Camión CAEX, Pala, Correa transportadora, Molino SAG, PLC, SCADA, etc.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Camión CAEX; Correa transportadora; Molino SAG; Servidor SCADA</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; Fact_OrdenesTrabajo.EquipmentID -&gt; EquipmentID; Fact_Costos.EquipmentID -&gt; EquipmentID; Fact_Mantenimiento.EquipmentID -&gt; EquipmentID; Fact_Incidentes.EquipmentID -&gt; EquipmentID; Fact_Energia.EquipmentID -&gt; EquipmentID</t>
         </is>
       </c>
     </row>
@@ -944,17 +1527,47 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>Activos mineros e industriales sinteticos, con criticidad y pertenencia a areas operacionales.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Una fila por activo físico, equipo minero, equipo de planta o sistema OT.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>Criticality</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Criticality de Dim_Equipo. Activos técnicos y criticidad.</t>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Criticidad operacional del equipo. Debe leerse como impacto potencial en producción, seguridad, costo o continuidad.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Crítica; Alta; Media; Baja</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; Fact_OrdenesTrabajo.EquipmentID -&gt; EquipmentID; Fact_Costos.EquipmentID -&gt; EquipmentID; Fact_Mantenimiento.EquipmentID -&gt; EquipmentID; Fact_Incidentes.EquipmentID -&gt; EquipmentID; Fact_Energia.EquipmentID -&gt; EquipmentID</t>
         </is>
       </c>
     </row>
@@ -971,17 +1584,47 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>Activos mineros e industriales sinteticos, con criticidad y pertenencia a areas operacionales.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Una fila por activo físico, equipo minero, equipo de planta o sistema OT.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>AreaID</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AreaID de Dim_Equipo. Activos técnicos y criticidad.</t>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Clave del área minera. En dimensiones es identificador; en hechos es llave foránea hacia Dim_Area.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Debe ser único si es PK y consistente si se usa como FK.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; Fact_OrdenesTrabajo.EquipmentID -&gt; EquipmentID; Fact_Costos.EquipmentID -&gt; EquipmentID; Fact_Mantenimiento.EquipmentID -&gt; EquipmentID; Fact_Incidentes.EquipmentID -&gt; EquipmentID; Fact_Energia.EquipmentID -&gt; EquipmentID</t>
         </is>
       </c>
     </row>
@@ -998,17 +1641,47 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>Activos mineros e industriales sinteticos, con criticidad y pertenencia a areas operacionales.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Una fila por activo físico, equipo minero, equipo de planta o sistema OT.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>Manufacturer</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Manufacturer de Dim_Equipo. Activos técnicos y criticidad.</t>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Fabricante ficticio del equipo. Sirve para segmentar sin usar marcas reales.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; Fact_OrdenesTrabajo.EquipmentID -&gt; EquipmentID; Fact_Costos.EquipmentID -&gt; EquipmentID; Fact_Mantenimiento.EquipmentID -&gt; EquipmentID; Fact_Incidentes.EquipmentID -&gt; EquipmentID; Fact_Energia.EquipmentID -&gt; EquipmentID</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1698,47 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>Activos mineros e industriales sinteticos, con criticidad y pertenencia a areas operacionales.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Una fila por activo físico, equipo minero, equipo de planta o sistema OT.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Model de Dim_Equipo. Activos técnicos y criticidad.</t>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Modelo ficticio del equipo.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; Fact_OrdenesTrabajo.EquipmentID -&gt; EquipmentID; Fact_Costos.EquipmentID -&gt; EquipmentID; Fact_Mantenimiento.EquipmentID -&gt; EquipmentID; Fact_Incidentes.EquipmentID -&gt; EquipmentID; Fact_Energia.EquipmentID -&gt; EquipmentID</t>
         </is>
       </c>
     </row>
@@ -1052,17 +1755,47 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>Activos mineros e industriales sinteticos, con criticidad y pertenencia a areas operacionales.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Una fila por activo físico, equipo minero, equipo de planta o sistema OT.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>CommissioningDate</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>CommissioningDate de Dim_Equipo. Activos técnicos y criticidad.</t>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Fecha de puesta en servicio del equipo.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; Fact_OrdenesTrabajo.EquipmentID -&gt; EquipmentID; Fact_Costos.EquipmentID -&gt; EquipmentID; Fact_Mantenimiento.EquipmentID -&gt; EquipmentID; Fact_Incidentes.EquipmentID -&gt; EquipmentID; Fact_Energia.EquipmentID -&gt; EquipmentID</t>
         </is>
       </c>
     </row>
@@ -1079,17 +1812,47 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>Activos mineros e industriales sinteticos, con criticidad y pertenencia a areas operacionales.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Una fila por activo físico, equipo minero, equipo de planta o sistema OT.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>ActiveFlag</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>ActiveFlag de Dim_Equipo. Activos técnicos y criticidad.</t>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Indica si el equipo está activo en el periodo del dataset.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; Fact_OrdenesTrabajo.EquipmentID -&gt; EquipmentID; Fact_Costos.EquipmentID -&gt; EquipmentID; Fact_Mantenimiento.EquipmentID -&gt; EquipmentID; Fact_Incidentes.EquipmentID -&gt; EquipmentID; Fact_Energia.EquipmentID -&gt; EquipmentID</t>
         </is>
       </c>
     </row>
@@ -1106,17 +1869,47 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>Clientes internos o contratos sinteticos relacionados con mineria, servicios mineros y mantenimiento industrial.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Una fila por cliente interno, gerencia, superintendencia o contrato sintético.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>ClientID</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>ClientID de Dim_Cliente. Clientes sintéticos y segmentos.</t>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Clave del cliente interno, gerencia o contrato sintético.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Debe ser único si es PK y consistente si se usa como FK.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Dim_Proyecto.ClientID -&gt; ClientID; Fact_SLA.ClientID -&gt; ClientID</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1926,47 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>Clientes internos o contratos sinteticos relacionados con mineria, servicios mineros y mantenimiento industrial.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Una fila por cliente interno, gerencia, superintendencia o contrato sintético.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>ClientName</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>ClientName de Dim_Cliente. Clientes sintéticos y segmentos.</t>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Cliente interno o contrato ficticio relacionado con minería.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Dim_Proyecto.ClientID -&gt; ClientID; Fact_SLA.ClientID -&gt; ClientID</t>
         </is>
       </c>
     </row>
@@ -1160,17 +1983,47 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>Clientes internos o contratos sinteticos relacionados con mineria, servicios mineros y mantenimiento industrial.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Una fila por cliente interno, gerencia, superintendencia o contrato sintético.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>Segment</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Segment de Dim_Cliente. Clientes sintéticos y segmentos.</t>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Segmento del cliente: Minería, Servicios Mineros, Operaciones Industriales, Energía Industrial o Mantenimiento Industrial.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Dim_Proyecto.ClientID -&gt; ClientID; Fact_SLA.ClientID -&gt; ClientID</t>
         </is>
       </c>
     </row>
@@ -1187,17 +2040,47 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>Clientes internos o contratos sinteticos relacionados con mineria, servicios mineros y mantenimiento industrial.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Una fila por cliente interno, gerencia, superintendencia o contrato sintético.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Region de Dim_Cliente. Clientes sintéticos y segmentos.</t>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Región ficticia de gestión. No corresponde a una localización real exacta.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Dim_Proyecto.ClientID -&gt; ClientID; Fact_SLA.ClientID -&gt; ClientID</t>
         </is>
       </c>
     </row>
@@ -1214,17 +2097,47 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>Clientes internos o contratos sinteticos relacionados con mineria, servicios mineros y mantenimiento industrial.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Una fila por cliente interno, gerencia, superintendencia o contrato sintético.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>ContractType</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>ContractType de Dim_Cliente. Clientes sintéticos y segmentos.</t>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tipo de relación: SLA operacional, proyecto mina, contrato marco o servicio especializado.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Dim_Proyecto.ClientID -&gt; ClientID; Fact_SLA.ClientID -&gt; ClientID</t>
         </is>
       </c>
     </row>
@@ -1241,17 +2154,47 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>Proyectos mineros sinteticos de confiabilidad, produccion, energia, seguridad, automatizacion e infraestructura.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Una fila por proyecto minero o iniciativa Tech&amp;Eng.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>ProjectID</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>ProjectID de Dim_Proyecto. Proyectos técnicos planificados.</t>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Clave del proyecto minero sintético.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Debe ser único si es PK y consistente si se usa como FK.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ClientID -&gt; Dim_Cliente.ClientID; AreaID -&gt; Dim_Area.AreaID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; PriorityID -&gt; Dim_Prioridad.PriorityID; Fact_Proyectos.ProjectID -&gt; ProjectID; Fact_Costos.ProjectID -&gt; ProjectID</t>
         </is>
       </c>
     </row>
@@ -1268,17 +2211,47 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>Proyectos mineros sinteticos de confiabilidad, produccion, energia, seguridad, automatizacion e infraestructura.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Una fila por proyecto minero o iniciativa Tech&amp;Eng.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>ProjectName</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>ProjectName de Dim_Proyecto. Proyectos técnicos planificados.</t>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nombre de iniciativa minera, por ejemplo reemplazo de correa, upgrade SCADA o reducción de consumo energético.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ClientID -&gt; Dim_Cliente.ClientID; AreaID -&gt; Dim_Area.AreaID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; PriorityID -&gt; Dim_Prioridad.PriorityID; Fact_Proyectos.ProjectID -&gt; ProjectID; Fact_Costos.ProjectID -&gt; ProjectID</t>
         </is>
       </c>
     </row>
@@ -1295,17 +2268,47 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>Proyectos mineros sinteticos de confiabilidad, produccion, energia, seguridad, automatizacion e infraestructura.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Una fila por proyecto minero o iniciativa Tech&amp;Eng.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>ProjectType</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>ProjectType de Dim_Proyecto. Proyectos técnicos planificados.</t>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tipo de proyecto: confiabilidad, energía, seguridad, producción, mantenimiento, automatización, infraestructura, planta, mina o transformación digital.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ClientID -&gt; Dim_Cliente.ClientID; AreaID -&gt; Dim_Area.AreaID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; PriorityID -&gt; Dim_Prioridad.PriorityID; Fact_Proyectos.ProjectID -&gt; ProjectID; Fact_Costos.ProjectID -&gt; ProjectID</t>
         </is>
       </c>
     </row>
@@ -1322,17 +2325,47 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>Proyectos mineros sinteticos de confiabilidad, produccion, energia, seguridad, automatizacion e infraestructura.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Una fila por proyecto minero o iniciativa Tech&amp;Eng.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>ClientID</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>ClientID de Dim_Proyecto. Proyectos técnicos planificados.</t>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Clave del cliente interno, gerencia o contrato sintético.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Debe ser único si es PK y consistente si se usa como FK.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ClientID -&gt; Dim_Cliente.ClientID; AreaID -&gt; Dim_Area.AreaID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; PriorityID -&gt; Dim_Prioridad.PriorityID; Fact_Proyectos.ProjectID -&gt; ProjectID; Fact_Costos.ProjectID -&gt; ProjectID</t>
         </is>
       </c>
     </row>
@@ -1349,17 +2382,47 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>Proyectos mineros sinteticos de confiabilidad, produccion, energia, seguridad, automatizacion e infraestructura.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Una fila por proyecto minero o iniciativa Tech&amp;Eng.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>AreaID</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>AreaID de Dim_Proyecto. Proyectos técnicos planificados.</t>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Clave del área minera. En dimensiones es identificador; en hechos es llave foránea hacia Dim_Area.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Debe ser único si es PK y consistente si se usa como FK.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>ClientID -&gt; Dim_Cliente.ClientID; AreaID -&gt; Dim_Area.AreaID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; PriorityID -&gt; Dim_Prioridad.PriorityID; Fact_Proyectos.ProjectID -&gt; ProjectID; Fact_Costos.ProjectID -&gt; ProjectID</t>
         </is>
       </c>
     </row>
@@ -1376,17 +2439,47 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>Proyectos mineros sinteticos de confiabilidad, produccion, energia, seguridad, automatizacion e infraestructura.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Una fila por proyecto minero o iniciativa Tech&amp;Eng.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>ResponsibleID</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>ResponsibleID de Dim_Proyecto. Proyectos técnicos planificados.</t>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Clave del responsable o rol asignado.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Debe ser único si es PK y consistente si se usa como FK.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>ClientID -&gt; Dim_Cliente.ClientID; AreaID -&gt; Dim_Area.AreaID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; PriorityID -&gt; Dim_Prioridad.PriorityID; Fact_Proyectos.ProjectID -&gt; ProjectID; Fact_Costos.ProjectID -&gt; ProjectID</t>
         </is>
       </c>
     </row>
@@ -1403,17 +2496,47 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>Proyectos mineros sinteticos de confiabilidad, produccion, energia, seguridad, automatizacion e infraestructura.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Una fila por proyecto minero o iniciativa Tech&amp;Eng.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>PriorityID</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>PriorityID de Dim_Proyecto. Proyectos técnicos planificados.</t>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Clave de prioridad operacional.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Debe ser único si es PK y consistente si se usa como FK.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ClientID -&gt; Dim_Cliente.ClientID; AreaID -&gt; Dim_Area.AreaID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; PriorityID -&gt; Dim_Prioridad.PriorityID; Fact_Proyectos.ProjectID -&gt; ProjectID; Fact_Costos.ProjectID -&gt; ProjectID</t>
         </is>
       </c>
     </row>
@@ -1430,17 +2553,47 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>Proyectos mineros sinteticos de confiabilidad, produccion, energia, seguridad, automatizacion e infraestructura.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Una fila por proyecto minero o iniciativa Tech&amp;Eng.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>PlannedStartDate</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>PlannedStartDate de Dim_Proyecto. Proyectos técnicos planificados.</t>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Campo PlannedStartDate de Dim_Proyecto.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ClientID -&gt; Dim_Cliente.ClientID; AreaID -&gt; Dim_Area.AreaID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; PriorityID -&gt; Dim_Prioridad.PriorityID; Fact_Proyectos.ProjectID -&gt; ProjectID; Fact_Costos.ProjectID -&gt; ProjectID</t>
         </is>
       </c>
     </row>
@@ -1457,17 +2610,47 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>Proyectos mineros sinteticos de confiabilidad, produccion, energia, seguridad, automatizacion e infraestructura.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Una fila por proyecto minero o iniciativa Tech&amp;Eng.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>PlannedEndDate</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>PlannedEndDate de Dim_Proyecto. Proyectos técnicos planificados.</t>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Campo PlannedEndDate de Dim_Proyecto.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ClientID -&gt; Dim_Cliente.ClientID; AreaID -&gt; Dim_Area.AreaID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; PriorityID -&gt; Dim_Prioridad.PriorityID; Fact_Proyectos.ProjectID -&gt; ProjectID; Fact_Costos.ProjectID -&gt; ProjectID</t>
         </is>
       </c>
     </row>
@@ -1484,17 +2667,47 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>Roles sinteticos de operacion minera, mantenimiento, confiabilidad, energia, HSE, costos y OT.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Una fila por responsable o rol sintético.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>ResponsibleID</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>ResponsibleID de Dim_Responsable. Responsables sintéticos de operación y proyectos.</t>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Clave del responsable o rol asignado.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Debe ser único si es PK y consistente si se usa como FK.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Dim_Proyecto.ResponsibleID -&gt; ResponsibleID; Fact_OrdenesTrabajo.ResponsibleID -&gt; ResponsibleID; Fact_Productividad.ResponsibleID -&gt; ResponsibleID</t>
         </is>
       </c>
     </row>
@@ -1511,17 +2724,47 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>Roles sinteticos de operacion minera, mantenimiento, confiabilidad, energia, HSE, costos y OT.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Una fila por responsable o rol sintético.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>ResponsibleName</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>ResponsibleName de Dim_Responsable. Responsables sintéticos de operación y proyectos.</t>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Nombre sintético del responsable. No representa personas reales.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Dim_Proyecto.ResponsibleID -&gt; ResponsibleID; Fact_OrdenesTrabajo.ResponsibleID -&gt; ResponsibleID; Fact_Productividad.ResponsibleID -&gt; ResponsibleID</t>
         </is>
       </c>
     </row>
@@ -1538,17 +2781,47 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>Roles sinteticos de operacion minera, mantenimiento, confiabilidad, energia, HSE, costos y OT.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Una fila por responsable o rol sintético.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Role de Dim_Responsable. Responsables sintéticos de operación y proyectos.</t>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Rol operacional o analítico del responsable.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Dim_Proyecto.ResponsibleID -&gt; ResponsibleID; Fact_OrdenesTrabajo.ResponsibleID -&gt; ResponsibleID; Fact_Productividad.ResponsibleID -&gt; ResponsibleID</t>
         </is>
       </c>
     </row>
@@ -1565,17 +2838,47 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>Roles sinteticos de operacion minera, mantenimiento, confiabilidad, energia, HSE, costos y OT.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Una fila por responsable o rol sintético.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Team de Dim_Responsable. Responsables sintéticos de operación y proyectos.</t>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Equipo, turno o grupo de trabajo sintético.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Dim_Proyecto.ResponsibleID -&gt; ResponsibleID; Fact_OrdenesTrabajo.ResponsibleID -&gt; ResponsibleID; Fact_Productividad.ResponsibleID -&gt; ResponsibleID</t>
         </is>
       </c>
     </row>
@@ -1592,17 +2895,47 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>Roles sinteticos de operacion minera, mantenimiento, confiabilidad, energia, HSE, costos y OT.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Una fila por responsable o rol sintético.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>AreaID</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>AreaID de Dim_Responsable. Responsables sintéticos de operación y proyectos.</t>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Clave del área minera. En dimensiones es identificador; en hechos es llave foránea hacia Dim_Area.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Debe ser único si es PK y consistente si se usa como FK.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Dim_Proyecto.ResponsibleID -&gt; ResponsibleID; Fact_OrdenesTrabajo.ResponsibleID -&gt; ResponsibleID; Fact_Productividad.ResponsibleID -&gt; ResponsibleID</t>
         </is>
       </c>
     </row>
@@ -1619,17 +2952,47 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>Tipos de trabajo usados en mantenimiento y operacion minera: correctivo, preventivo, predictivo, inspeccion, paradas y emergencias.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Una fila por tipo de trabajo operacional o de mantenimiento.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>WorkTypeID</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>WorkTypeID de Dim_TipoTrabajo. Tipos de trabajo planificado y correctivo.</t>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Clave del tipo de trabajo.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Debe ser único si es PK y consistente si se usa como FK.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Fact_OrdenesTrabajo.WorkTypeID -&gt; WorkTypeID; Fact_Mantenimiento.WorkTypeID -&gt; WorkTypeID</t>
         </is>
       </c>
     </row>
@@ -1646,17 +3009,47 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>Tipos de trabajo usados en mantenimiento y operacion minera: correctivo, preventivo, predictivo, inspeccion, paradas y emergencias.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Una fila por tipo de trabajo operacional o de mantenimiento.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>WorkTypeName</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>WorkTypeName de Dim_TipoTrabajo. Tipos de trabajo planificado y correctivo.</t>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tipo de trabajo operacional o de mantenimiento.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Correctivo no planificado; Predictivo; Parada planta; Soporte OT</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Fact_OrdenesTrabajo.WorkTypeID -&gt; WorkTypeID; Fact_Mantenimiento.WorkTypeID -&gt; WorkTypeID</t>
         </is>
       </c>
     </row>
@@ -1673,17 +3066,47 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
+          <t>Tipos de trabajo usados en mantenimiento y operacion minera: correctivo, preventivo, predictivo, inspeccion, paradas y emergencias.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Una fila por tipo de trabajo operacional o de mantenimiento.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>WorkCategory</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>WorkCategory de Dim_TipoTrabajo. Tipos de trabajo planificado y correctivo.</t>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Categoría analítica del trabajo: Correctivo, Preventivo, Predictivo, Inspección, Proyecto, Emergencia o Mejora.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Fact_OrdenesTrabajo.WorkTypeID -&gt; WorkTypeID; Fact_Mantenimiento.WorkTypeID -&gt; WorkTypeID</t>
         </is>
       </c>
     </row>
@@ -1700,17 +3123,47 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
+          <t>Tipos de trabajo usados en mantenimiento y operacion minera: correctivo, preventivo, predictivo, inspeccion, paradas y emergencias.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Una fila por tipo de trabajo operacional o de mantenimiento.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>PlannedFlag</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>PlannedFlag de Dim_TipoTrabajo. Tipos de trabajo planificado y correctivo.</t>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Indica si el registro corresponde a trabajo planificado. En mantenimiento ayuda a separar preventivo/planificado de correctivo no planificado.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Fact_OrdenesTrabajo.WorkTypeID -&gt; WorkTypeID; Fact_Mantenimiento.WorkTypeID -&gt; WorkTypeID</t>
         </is>
       </c>
     </row>
@@ -1727,17 +3180,47 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>Prioridades operacionales y objetivos de respuesta/resolucion para servicios mineros.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Una fila por nivel de prioridad operacional.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>PriorityID</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>PriorityID de Dim_Prioridad. Prioridades y objetivos de respuesta/resolución.</t>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Clave de prioridad operacional.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Debe ser único si es PK y consistente si se usa como FK.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Dim_Proyecto.PriorityID -&gt; PriorityID; Fact_OrdenesTrabajo.PriorityID -&gt; PriorityID; Fact_SLA.PriorityID -&gt; PriorityID; Fact_Mantenimiento.PriorityID -&gt; PriorityID</t>
         </is>
       </c>
     </row>
@@ -1754,17 +3237,47 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>Prioridades operacionales y objetivos de respuesta/resolucion para servicios mineros.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Una fila por nivel de prioridad operacional.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>PriorityName</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>PriorityName de Dim_Prioridad. Prioridades y objetivos de respuesta/resolución.</t>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Nivel de prioridad estandarizado: Crítica, Alta, Media o Baja.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Dim_Proyecto.PriorityID -&gt; PriorityID; Fact_OrdenesTrabajo.PriorityID -&gt; PriorityID; Fact_SLA.PriorityID -&gt; PriorityID; Fact_Mantenimiento.PriorityID -&gt; PriorityID</t>
         </is>
       </c>
     </row>
@@ -1781,17 +3294,47 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>Prioridades operacionales y objetivos de respuesta/resolucion para servicios mineros.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Una fila por nivel de prioridad operacional.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>PriorityRank</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>PriorityRank de Dim_Prioridad. Prioridades y objetivos de respuesta/resolución.</t>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Orden numérico de prioridad. Menor valor significa mayor prioridad.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Dim_Proyecto.PriorityID -&gt; PriorityID; Fact_OrdenesTrabajo.PriorityID -&gt; PriorityID; Fact_SLA.PriorityID -&gt; PriorityID; Fact_Mantenimiento.PriorityID -&gt; PriorityID</t>
         </is>
       </c>
     </row>
@@ -1808,17 +3351,47 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
+          <t>Prioridades operacionales y objetivos de respuesta/resolucion para servicios mineros.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Una fila por nivel de prioridad operacional.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>TargetResponseHours</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>TargetResponseHours de Dim_Prioridad. Prioridades y objetivos de respuesta/resolución.</t>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Horas objetivo para responder a una solicitud según prioridad.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Dim_Proyecto.PriorityID -&gt; PriorityID; Fact_OrdenesTrabajo.PriorityID -&gt; PriorityID; Fact_SLA.PriorityID -&gt; PriorityID; Fact_Mantenimiento.PriorityID -&gt; PriorityID</t>
         </is>
       </c>
     </row>
@@ -1835,17 +3408,47 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>Prioridades operacionales y objetivos de respuesta/resolucion para servicios mineros.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Una fila por nivel de prioridad operacional.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>TargetResolutionHours</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>TargetResolutionHours de Dim_Prioridad. Prioridades y objetivos de respuesta/resolución.</t>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Horas objetivo para resolver una solicitud según prioridad.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Dim_Proyecto.PriorityID -&gt; PriorityID; Fact_OrdenesTrabajo.PriorityID -&gt; PriorityID; Fact_SLA.PriorityID -&gt; PriorityID; Fact_Mantenimiento.PriorityID -&gt; PriorityID</t>
         </is>
       </c>
     </row>
@@ -1862,17 +3465,47 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>Estados estandarizados para ordenes, proyectos y acciones operacionales.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Una fila por estado estandarizado.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>StatusID</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>StatusID de Dim_Estado. Estados operativos y grupos de cierre.</t>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Clave de estado estandarizado.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Debe ser único si es PK y consistente si se usa como FK.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Fact_OrdenesTrabajo.StatusID -&gt; StatusID</t>
         </is>
       </c>
     </row>
@@ -1889,17 +3522,47 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>Estados estandarizados para ordenes, proyectos y acciones operacionales.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Una fila por estado estandarizado.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>StatusName</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>StatusName de Dim_Estado. Estados operativos y grupos de cierre.</t>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Estado operacional estandarizado: Abierta, En Proceso, Vencida, Cerrada o Cancelada.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Fact_OrdenesTrabajo.StatusID -&gt; StatusID</t>
         </is>
       </c>
     </row>
@@ -1916,17 +3579,47 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>Estados estandarizados para ordenes, proyectos y acciones operacionales.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Una fila por estado estandarizado.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>StatusGroup</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>StatusGroup de Dim_Estado. Estados operativos y grupos de cierre.</t>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Grupo de análisis del estado: abierto, cerrado, vencido u otro.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Fact_OrdenesTrabajo.StatusID -&gt; StatusID</t>
         </is>
       </c>
     </row>
@@ -1943,17 +3636,47 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>Estados estandarizados para ordenes, proyectos y acciones operacionales.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Una fila por estado estandarizado.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>SortOrder</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>SortOrder de Dim_Estado. Estados operativos y grupos de cierre.</t>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Orden recomendado para mostrar estados en reportes.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Fact_OrdenesTrabajo.StatusID -&gt; StatusID</t>
         </is>
       </c>
     </row>
@@ -1970,17 +3693,47 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>Estados estandarizados para ordenes, proyectos y acciones operacionales.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Una fila por estado estandarizado.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>IsClosed</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>IsClosed de Dim_Estado. Estados operativos y grupos de cierre.</t>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Indica si el estado se considera cerrado para KPIs de backlog o cumplimiento.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Fact_OrdenesTrabajo.StatusID -&gt; StatusID</t>
         </is>
       </c>
     </row>
@@ -1997,17 +3750,47 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
+          <t>Servicios mineros gestionados con SLA: mantenimiento mina/planta, dispatch, correas, SCADA, energia, HSE y relaves.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Una fila por servicio operacional sujeto a SLA.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>ServiceID</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>ServiceID de Dim_Servicio. Servicios gestionados y SLA por defecto.</t>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Clave del servicio operacional.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Debe ser único si es PK y consistente si se usa como FK.</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Fact_OrdenesTrabajo.ServiceID -&gt; ServiceID; Fact_SLA.ServiceID -&gt; ServiceID</t>
         </is>
       </c>
     </row>
@@ -2024,17 +3807,47 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
+          <t>Servicios mineros gestionados con SLA: mantenimiento mina/planta, dispatch, correas, SCADA, energia, HSE y relaves.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Una fila por servicio operacional sujeto a SLA.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>ServiceName</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>ServiceName de Dim_Servicio. Servicios gestionados y SLA por defecto.</t>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Servicio minero sujeto a gestión o SLA, por ejemplo Mantenimiento Planta, Soporte Dispatch o Gestión de Relaves.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Soporte Dispatch; Inspección de Correas; Gestión de Relaves</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Fact_OrdenesTrabajo.ServiceID -&gt; ServiceID; Fact_SLA.ServiceID -&gt; ServiceID</t>
         </is>
       </c>
     </row>
@@ -2051,17 +3864,47 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
+          <t>Servicios mineros gestionados con SLA: mantenimiento mina/planta, dispatch, correas, SCADA, energia, HSE y relaves.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Una fila por servicio operacional sujeto a SLA.</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>ServiceCategory</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>ServiceCategory de Dim_Servicio. Servicios gestionados y SLA por defecto.</t>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Categoría del servicio: Mina, Planta, Mantenimiento, Energía, Seguridad, Automatización, Operaciones o Ingeniería.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Fact_OrdenesTrabajo.ServiceID -&gt; ServiceID; Fact_SLA.ServiceID -&gt; ServiceID</t>
         </is>
       </c>
     </row>
@@ -2078,17 +3921,47 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
+          <t>Servicios mineros gestionados con SLA: mantenimiento mina/planta, dispatch, correas, SCADA, energia, HSE y relaves.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Una fila por servicio operacional sujeto a SLA.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
           <t>DefaultSLAHours</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>DefaultSLAHours de Dim_Servicio. Servicios gestionados y SLA por defecto.</t>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Horas SLA por defecto del servicio antes de ajustar por prioridad o contexto.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Fact_OrdenesTrabajo.ServiceID -&gt; ServiceID; Fact_SLA.ServiceID -&gt; ServiceID</t>
         </is>
       </c>
     </row>
@@ -2105,17 +3978,47 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
+          <t>Ubicaciones sinteticas de faena: pit, frentes, chancado, correas, molinos, relaves, salas electricas y talleres.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Una fila por ubicación física sintética de faena.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>LocationID</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>LocationID de Dim_Ubicacion. Ubicaciones sintéticas.</t>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Clave de ubicación. En dimensiones es identificador; en hechos permite analizar por lugar físico de faena.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Debe ser único si es PK y consistente si se usa como FK.</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Dim_Area.LocationID -&gt; LocationID; Fact_Incidentes.LocationID -&gt; LocationID; Fact_Energia.LocationID -&gt; LocationID; Fact_Productividad.LocationID -&gt; LocationID</t>
         </is>
       </c>
     </row>
@@ -2132,17 +4035,47 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>Ubicaciones sinteticas de faena: pit, frentes, chancado, correas, molinos, relaves, salas electricas y talleres.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Una fila por ubicación física sintética de faena.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>LocationName</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>LocationName de Dim_Ubicacion. Ubicaciones sintéticas.</t>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Nombre de ubicación física sintética: Pit Norte, Faja CV-101, Molino SAG, Relavera Principal, etc.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Dim_Area.LocationID -&gt; LocationID; Fact_Incidentes.LocationID -&gt; LocationID; Fact_Energia.LocationID -&gt; LocationID; Fact_Productividad.LocationID -&gt; LocationID</t>
         </is>
       </c>
     </row>
@@ -2159,17 +4092,47 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
+          <t>Ubicaciones sinteticas de faena: pit, frentes, chancado, correas, molinos, relaves, salas electricas y talleres.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Una fila por ubicación física sintética de faena.</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>Site</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Site de Dim_Ubicacion. Ubicaciones sintéticas.</t>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Nombre ficticio del sitio minero. No corresponde a una faena real.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sitio Andina Norte; Sitio Pampa Central; Sitio Sierra Azul</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Dim_Area.LocationID -&gt; LocationID; Fact_Incidentes.LocationID -&gt; LocationID; Fact_Energia.LocationID -&gt; LocationID; Fact_Productividad.LocationID -&gt; LocationID</t>
         </is>
       </c>
     </row>
@@ -2186,17 +4149,47 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
+          <t>Ubicaciones sinteticas de faena: pit, frentes, chancado, correas, molinos, relaves, salas electricas y talleres.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Una fila por ubicación física sintética de faena.</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Zone de Dim_Ubicacion. Ubicaciones sintéticas.</t>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Zona operacional de la ubicación: Mina, Planta, Relaves, Energía, Mantenimiento, Control u Operaciones.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Dim_Area.LocationID -&gt; LocationID; Fact_Incidentes.LocationID -&gt; LocationID; Fact_Energia.LocationID -&gt; LocationID; Fact_Productividad.LocationID -&gt; LocationID</t>
         </is>
       </c>
     </row>
@@ -2213,17 +4206,47 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
+          <t>Ubicaciones sinteticas de faena: pit, frentes, chancado, correas, molinos, relaves, salas electricas y talleres.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Una fila por ubicación física sintética de faena.</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Country de Dim_Ubicacion. Ubicaciones sintéticas.</t>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>País ficticio/operacional usado para el caso. No implica uso de datos reales.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Segmentación, filtros, relaciones o validación del modelo.</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>En clean está estandarizado; en raw puede tener variaciones controladas para práctica de Power Query.</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Dim_Area.LocationID -&gt; LocationID; Fact_Incidentes.LocationID -&gt; LocationID; Fact_Energia.LocationID -&gt; LocationID; Fact_Productividad.LocationID -&gt; LocationID</t>
         </is>
       </c>
     </row>
@@ -2240,17 +4263,47 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
+          <t>Avance, costo, riesgo y retraso de proyectos mineros sinteticos.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Una fila por corte de seguimiento de proyecto.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>ProjectFactID</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>ProjectFactID de Fact_Proyectos. Avance, costo y riesgo de proyectos.</t>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Clave del registro de seguimiento del proyecto.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Avance real vs plan, delay days, cost variance, risk score y cumplimiento de presupuesto.</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>ProjectID -&gt; Dim_Proyecto.ProjectID; DateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID</t>
         </is>
       </c>
     </row>
@@ -2267,17 +4320,47 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
+          <t>Avance, costo, riesgo y retraso de proyectos mineros sinteticos.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Una fila por corte de seguimiento de proyecto.</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>ProjectID</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>ProjectID de Fact_Proyectos. Avance, costo y riesgo de proyectos.</t>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Clave del proyecto minero sintético.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Avance real vs plan, delay days, cost variance, risk score y cumplimiento de presupuesto.</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>ProjectID -&gt; Dim_Proyecto.ProjectID; DateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID</t>
         </is>
       </c>
     </row>
@@ -2294,17 +4377,47 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
+          <t>Avance, costo, riesgo y retraso de proyectos mineros sinteticos.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Una fila por corte de seguimiento de proyecto.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
           <t>DateKey</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>DateKey de Fact_Proyectos. Avance, costo y riesgo de proyectos.</t>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Clave de fecha en formato yyyymmdd. Permite relacionar hechos con Dim_Fecha sin depender de formatos regionales.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Avance real vs plan, delay days, cost variance, risk score y cumplimiento de presupuesto.</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>ProjectID -&gt; Dim_Proyecto.ProjectID; DateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID</t>
         </is>
       </c>
     </row>
@@ -2321,17 +4434,47 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
+          <t>Avance, costo, riesgo y retraso de proyectos mineros sinteticos.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Una fila por corte de seguimiento de proyecto.</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>AreaID</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AreaID de Fact_Proyectos. Avance, costo y riesgo de proyectos.</t>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Clave del área minera. En dimensiones es identificador; en hechos es llave foránea hacia Dim_Area.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Avance real vs plan, delay days, cost variance, risk score y cumplimiento de presupuesto.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>ProjectID -&gt; Dim_Proyecto.ProjectID; DateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID</t>
         </is>
       </c>
     </row>
@@ -2348,17 +4491,47 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
+          <t>Avance, costo, riesgo y retraso de proyectos mineros sinteticos.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Una fila por corte de seguimiento de proyecto.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>ClientID</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>ClientID de Fact_Proyectos. Avance, costo y riesgo de proyectos.</t>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Clave del cliente interno, gerencia o contrato sintético.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Avance real vs plan, delay days, cost variance, risk score y cumplimiento de presupuesto.</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>ProjectID -&gt; Dim_Proyecto.ProjectID; DateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID</t>
         </is>
       </c>
     </row>
@@ -2375,17 +4548,47 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
+          <t>Avance, costo, riesgo y retraso de proyectos mineros sinteticos.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Una fila por corte de seguimiento de proyecto.</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
           <t>ResponsibleID</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>ResponsibleID de Fact_Proyectos. Avance, costo y riesgo de proyectos.</t>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Clave del responsable o rol asignado.</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Avance real vs plan, delay days, cost variance, risk score y cumplimiento de presupuesto.</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>ProjectID -&gt; Dim_Proyecto.ProjectID; DateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID</t>
         </is>
       </c>
     </row>
@@ -2402,17 +4605,47 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
+          <t>Avance, costo, riesgo y retraso de proyectos mineros sinteticos.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Una fila por corte de seguimiento de proyecto.</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
           <t>StatusID</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>StatusID de Fact_Proyectos. Avance, costo y riesgo de proyectos.</t>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Clave de estado estandarizado.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Avance real vs plan, delay days, cost variance, risk score y cumplimiento de presupuesto.</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>ProjectID -&gt; Dim_Proyecto.ProjectID; DateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID</t>
         </is>
       </c>
     </row>
@@ -2429,17 +4662,47 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
+          <t>Avance, costo, riesgo y retraso de proyectos mineros sinteticos.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Una fila por corte de seguimiento de proyecto.</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>PriorityID</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>PriorityID de Fact_Proyectos. Avance, costo y riesgo de proyectos.</t>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Clave de prioridad operacional.</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Avance real vs plan, delay days, cost variance, risk score y cumplimiento de presupuesto.</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>ProjectID -&gt; Dim_Proyecto.ProjectID; DateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID</t>
         </is>
       </c>
     </row>
@@ -2456,17 +4719,47 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
+          <t>Avance, costo, riesgo y retraso de proyectos mineros sinteticos.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Una fila por corte de seguimiento de proyecto.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>PlannedProgressPct</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>PlannedProgressPct de Fact_Proyectos. Avance, costo y riesgo de proyectos.</t>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Avance planificado del proyecto a la fecha del registro.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Avance real vs plan, delay days, cost variance, risk score y cumplimiento de presupuesto.</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>ProjectID -&gt; Dim_Proyecto.ProjectID; DateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID</t>
         </is>
       </c>
     </row>
@@ -2483,17 +4776,47 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
+          <t>Avance, costo, riesgo y retraso de proyectos mineros sinteticos.</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Una fila por corte de seguimiento de proyecto.</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
           <t>ActualProgressPct</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>ActualProgressPct de Fact_Proyectos. Avance, costo y riesgo de proyectos.</t>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Avance real del proyecto a la fecha del registro.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Avance real vs plan, delay days, cost variance, risk score y cumplimiento de presupuesto.</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>ProjectID -&gt; Dim_Proyecto.ProjectID; DateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID</t>
         </is>
       </c>
     </row>
@@ -2510,17 +4833,47 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
+          <t>Avance, costo, riesgo y retraso de proyectos mineros sinteticos.</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Una fila por corte de seguimiento de proyecto.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>PlannedCost</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>PlannedCost de Fact_Proyectos. Avance, costo y riesgo de proyectos.</t>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Costo planificado o presupuesto del proyecto.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Avance real vs plan, delay days, cost variance, risk score y cumplimiento de presupuesto.</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>ProjectID -&gt; Dim_Proyecto.ProjectID; DateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID</t>
         </is>
       </c>
     </row>
@@ -2537,17 +4890,47 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
+          <t>Avance, costo, riesgo y retraso de proyectos mineros sinteticos.</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Una fila por corte de seguimiento de proyecto.</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
           <t>ActualCost</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>ActualCost de Fact_Proyectos. Avance, costo y riesgo de proyectos.</t>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Costo real acumulado o registrado del proyecto.</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Avance real vs plan, delay days, cost variance, risk score y cumplimiento de presupuesto.</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>ProjectID -&gt; Dim_Proyecto.ProjectID; DateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID</t>
         </is>
       </c>
     </row>
@@ -2564,17 +4947,47 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
+          <t>Avance, costo, riesgo y retraso de proyectos mineros sinteticos.</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Una fila por corte de seguimiento de proyecto.</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>RiskScore</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>RiskScore de Fact_Proyectos. Avance, costo y riesgo de proyectos.</t>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Puntaje sintético de riesgo del proyecto. Valores más altos sugieren mayor probabilidad de atraso, sobrecosto o impacto operacional.</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Avance real vs plan, delay days, cost variance, risk score y cumplimiento de presupuesto.</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>ProjectID -&gt; Dim_Proyecto.ProjectID; DateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID</t>
         </is>
       </c>
     </row>
@@ -2591,17 +5004,47 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
+          <t>Avance, costo, riesgo y retraso de proyectos mineros sinteticos.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Una fila por corte de seguimiento de proyecto.</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>DelayDays</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>DelayDays de Fact_Proyectos. Avance, costo y riesgo de proyectos.</t>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Días de retraso del proyecto frente al plan. Cero indica sin retraso registrado.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Avance real vs plan, delay days, cost variance, risk score y cumplimiento de presupuesto.</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>ProjectID -&gt; Dim_Proyecto.ProjectID; DateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID</t>
         </is>
       </c>
     </row>
@@ -2618,17 +5061,47 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
+          <t>Ordenes de trabajo de mantenimiento, operaciones y soporte OT con backlog, criticidad y fuente de sistema.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Una fila por orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>WorkOrderID</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>WorkOrderID de Fact_OrdenesTrabajo. Órdenes de trabajo técnicas.</t>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Clave de la orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Backlog, órdenes críticas abiertas, retrabajo, horas reales vs estimadas y carga por sistema fuente.</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; CreatedDateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID; ServiceID -&gt; Dim_Servicio.ServiceID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; StatusID -&gt; Dim_Estado.StatusID; Fact_SLA.WorkOrderID -&gt; WorkOrderID</t>
         </is>
       </c>
     </row>
@@ -2645,17 +5118,47 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
+          <t>Ordenes de trabajo de mantenimiento, operaciones y soporte OT con backlog, criticidad y fuente de sistema.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Una fila por orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>CreatedDateKey</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>CreatedDateKey de Fact_OrdenesTrabajo. Órdenes de trabajo técnicas.</t>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Fecha de creación de la orden o del compromiso SLA.</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Backlog, órdenes críticas abiertas, retrabajo, horas reales vs estimadas y carga por sistema fuente.</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; CreatedDateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID; ServiceID -&gt; Dim_Servicio.ServiceID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; StatusID -&gt; Dim_Estado.StatusID; Fact_SLA.WorkOrderID -&gt; WorkOrderID</t>
         </is>
       </c>
     </row>
@@ -2672,17 +5175,47 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
+          <t>Ordenes de trabajo de mantenimiento, operaciones y soporte OT con backlog, criticidad y fuente de sistema.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Una fila por orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
           <t>ClosedDateKey</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>ClosedDateKey de Fact_OrdenesTrabajo. Órdenes de trabajo técnicas.</t>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Fecha de cierre de la orden. En raw puede venir nula para prácticas de limpieza.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Backlog, órdenes críticas abiertas, retrabajo, horas reales vs estimadas y carga por sistema fuente.</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>En raw puede aparecer nulo o con formato inconsistente; en clean debe permitir análisis de cierre/resolución.</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; CreatedDateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID; ServiceID -&gt; Dim_Servicio.ServiceID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; StatusID -&gt; Dim_Estado.StatusID; Fact_SLA.WorkOrderID -&gt; WorkOrderID</t>
         </is>
       </c>
     </row>
@@ -2699,17 +5232,47 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
+          <t>Ordenes de trabajo de mantenimiento, operaciones y soporte OT con backlog, criticidad y fuente de sistema.</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Una fila por orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>AreaID</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AreaID de Fact_OrdenesTrabajo. Órdenes de trabajo técnicas.</t>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Clave del área minera. En dimensiones es identificador; en hechos es llave foránea hacia Dim_Area.</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Backlog, órdenes críticas abiertas, retrabajo, horas reales vs estimadas y carga por sistema fuente.</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; CreatedDateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID; ServiceID -&gt; Dim_Servicio.ServiceID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; StatusID -&gt; Dim_Estado.StatusID; Fact_SLA.WorkOrderID -&gt; WorkOrderID</t>
         </is>
       </c>
     </row>
@@ -2726,17 +5289,47 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
+          <t>Ordenes de trabajo de mantenimiento, operaciones y soporte OT con backlog, criticidad y fuente de sistema.</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Una fila por orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
           <t>EquipmentID</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>EquipmentID de Fact_OrdenesTrabajo. Órdenes de trabajo técnicas.</t>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Clave del equipo o activo. En hechos permite conectar costos, mantenimiento, energía e incidentes con Dim_Equipo.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Backlog, órdenes críticas abiertas, retrabajo, horas reales vs estimadas y carga por sistema fuente.</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; CreatedDateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID; ServiceID -&gt; Dim_Servicio.ServiceID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; StatusID -&gt; Dim_Estado.StatusID; Fact_SLA.WorkOrderID -&gt; WorkOrderID</t>
         </is>
       </c>
     </row>
@@ -2753,17 +5346,47 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
+          <t>Ordenes de trabajo de mantenimiento, operaciones y soporte OT con backlog, criticidad y fuente de sistema.</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Una fila por orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>ServiceID</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>ServiceID de Fact_OrdenesTrabajo. Órdenes de trabajo técnicas.</t>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Clave del servicio operacional.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Backlog, órdenes críticas abiertas, retrabajo, horas reales vs estimadas y carga por sistema fuente.</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; CreatedDateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID; ServiceID -&gt; Dim_Servicio.ServiceID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; StatusID -&gt; Dim_Estado.StatusID; Fact_SLA.WorkOrderID -&gt; WorkOrderID</t>
         </is>
       </c>
     </row>
@@ -2780,17 +5403,47 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
+          <t>Ordenes de trabajo de mantenimiento, operaciones y soporte OT con backlog, criticidad y fuente de sistema.</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Una fila por orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>ResponsibleID</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>ResponsibleID de Fact_OrdenesTrabajo. Órdenes de trabajo técnicas.</t>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Clave del responsable o rol asignado.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Backlog, órdenes críticas abiertas, retrabajo, horas reales vs estimadas y carga por sistema fuente.</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; CreatedDateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID; ServiceID -&gt; Dim_Servicio.ServiceID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; StatusID -&gt; Dim_Estado.StatusID; Fact_SLA.WorkOrderID -&gt; WorkOrderID</t>
         </is>
       </c>
     </row>
@@ -2807,17 +5460,47 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
+          <t>Ordenes de trabajo de mantenimiento, operaciones y soporte OT con backlog, criticidad y fuente de sistema.</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Una fila por orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
           <t>WorkTypeID</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>WorkTypeID de Fact_OrdenesTrabajo. Órdenes de trabajo técnicas.</t>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Clave del tipo de trabajo.</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Backlog, órdenes críticas abiertas, retrabajo, horas reales vs estimadas y carga por sistema fuente.</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; CreatedDateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID; ServiceID -&gt; Dim_Servicio.ServiceID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; StatusID -&gt; Dim_Estado.StatusID; Fact_SLA.WorkOrderID -&gt; WorkOrderID</t>
         </is>
       </c>
     </row>
@@ -2834,17 +5517,47 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
+          <t>Ordenes de trabajo de mantenimiento, operaciones y soporte OT con backlog, criticidad y fuente de sistema.</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Una fila por orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>PriorityID</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>PriorityID de Fact_OrdenesTrabajo. Órdenes de trabajo técnicas.</t>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Clave de prioridad operacional.</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Backlog, órdenes críticas abiertas, retrabajo, horas reales vs estimadas y carga por sistema fuente.</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; CreatedDateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID; ServiceID -&gt; Dim_Servicio.ServiceID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; StatusID -&gt; Dim_Estado.StatusID; Fact_SLA.WorkOrderID -&gt; WorkOrderID</t>
         </is>
       </c>
     </row>
@@ -2861,17 +5574,47 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
+          <t>Ordenes de trabajo de mantenimiento, operaciones y soporte OT con backlog, criticidad y fuente de sistema.</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Una fila por orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
           <t>StatusID</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>StatusID de Fact_OrdenesTrabajo. Órdenes de trabajo técnicas.</t>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Clave de estado estandarizado.</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Backlog, órdenes críticas abiertas, retrabajo, horas reales vs estimadas y carga por sistema fuente.</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; CreatedDateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID; ServiceID -&gt; Dim_Servicio.ServiceID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; StatusID -&gt; Dim_Estado.StatusID; Fact_SLA.WorkOrderID -&gt; WorkOrderID</t>
         </is>
       </c>
     </row>
@@ -2888,17 +5631,47 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
+          <t>Ordenes de trabajo de mantenimiento, operaciones y soporte OT con backlog, criticidad y fuente de sistema.</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Una fila por orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
           <t>EstimatedHours</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>EstimatedHours de Fact_OrdenesTrabajo. Órdenes de trabajo técnicas.</t>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Horas estimadas antes de ejecutar la orden.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Backlog, órdenes críticas abiertas, retrabajo, horas reales vs estimadas y carga por sistema fuente.</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; CreatedDateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID; ServiceID -&gt; Dim_Servicio.ServiceID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; StatusID -&gt; Dim_Estado.StatusID; Fact_SLA.WorkOrderID -&gt; WorkOrderID</t>
         </is>
       </c>
     </row>
@@ -2915,17 +5688,47 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
+          <t>Ordenes de trabajo de mantenimiento, operaciones y soporte OT con backlog, criticidad y fuente de sistema.</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Una fila por orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
           <t>ActualHours</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>ActualHours de Fact_OrdenesTrabajo. Órdenes de trabajo técnicas.</t>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Horas reales consumidas por la orden o el SLA.</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Backlog, órdenes críticas abiertas, retrabajo, horas reales vs estimadas y carga por sistema fuente.</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; CreatedDateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID; ServiceID -&gt; Dim_Servicio.ServiceID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; StatusID -&gt; Dim_Estado.StatusID; Fact_SLA.WorkOrderID -&gt; WorkOrderID</t>
         </is>
       </c>
     </row>
@@ -2942,17 +5745,47 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
+          <t>Ordenes de trabajo de mantenimiento, operaciones y soporte OT con backlog, criticidad y fuente de sistema.</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Una fila por orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>IsCritical</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>IsCritical de Fact_OrdenesTrabajo. Órdenes de trabajo técnicas.</t>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Marca órdenes críticas por impacto operacional, seguridad, continuidad o SLA.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Backlog, órdenes críticas abiertas, retrabajo, horas reales vs estimadas y carga por sistema fuente.</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; CreatedDateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID; ServiceID -&gt; Dim_Servicio.ServiceID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; StatusID -&gt; Dim_Estado.StatusID; Fact_SLA.WorkOrderID -&gt; WorkOrderID</t>
         </is>
       </c>
     </row>
@@ -2969,17 +5802,47 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
+          <t>Ordenes de trabajo de mantenimiento, operaciones y soporte OT con backlog, criticidad y fuente de sistema.</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Una fila por orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
           <t>ReworkFlag</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>ReworkFlag de Fact_OrdenesTrabajo. Órdenes de trabajo técnicas.</t>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Indica retrabajo. Es útil para detectar problemas repetitivos de calidad, planificación o mantenimiento.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Backlog, órdenes críticas abiertas, retrabajo, horas reales vs estimadas y carga por sistema fuente.</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; CreatedDateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID; ServiceID -&gt; Dim_Servicio.ServiceID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; StatusID -&gt; Dim_Estado.StatusID; Fact_SLA.WorkOrderID -&gt; WorkOrderID</t>
         </is>
       </c>
     </row>
@@ -2996,17 +5859,47 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
+          <t>Ordenes de trabajo de mantenimiento, operaciones y soporte OT con backlog, criticidad y fuente de sistema.</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Una fila por orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
           <t>SourceSystem</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>SourceSystem de Fact_OrdenesTrabajo. Órdenes de trabajo técnicas.</t>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Sistema fuente sintético: SAP PM, Maximo, SCADA, Dispatch o Excel Manual.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>SAP PM; Maximo; SCADA; Dispatch; Excel Manual</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Backlog, órdenes críticas abiertas, retrabajo, horas reales vs estimadas y carga por sistema fuente.</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; CreatedDateKey -&gt; Dim_Fecha.DateKey; AreaID -&gt; Dim_Area.AreaID; ServiceID -&gt; Dim_Servicio.ServiceID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; StatusID -&gt; Dim_Estado.StatusID; Fact_SLA.WorkOrderID -&gt; WorkOrderID</t>
         </is>
       </c>
     </row>
@@ -3023,17 +5916,47 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
+          <t>Presupuesto, comprometido y costo real de operacion, mantenimiento, energia, repuestos, contratistas y proyectos mineros.</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Una fila por registro de costo presupuestado, comprometido y real.</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
           <t>CostID</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>CostID de Fact_Costos. Presupuesto, comprometido y costo real.</t>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Clave del registro de costo.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Costo real vs presupuesto, variación de costo, costo por área/equipo/proyecto.</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>ProjectID -&gt; Dim_Proyecto.ProjectID; EquipmentID -&gt; Dim_Equipo.EquipmentID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3050,17 +5973,47 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
+          <t>Presupuesto, comprometido y costo real de operacion, mantenimiento, energia, repuestos, contratistas y proyectos mineros.</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Una fila por registro de costo presupuestado, comprometido y real.</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
           <t>DateKey</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>DateKey de Fact_Costos. Presupuesto, comprometido y costo real.</t>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Clave de fecha en formato yyyymmdd. Permite relacionar hechos con Dim_Fecha sin depender de formatos regionales.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Costo real vs presupuesto, variación de costo, costo por área/equipo/proyecto.</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>ProjectID -&gt; Dim_Proyecto.ProjectID; EquipmentID -&gt; Dim_Equipo.EquipmentID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3077,17 +6030,47 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
+          <t>Presupuesto, comprometido y costo real de operacion, mantenimiento, energia, repuestos, contratistas y proyectos mineros.</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Una fila por registro de costo presupuestado, comprometido y real.</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
           <t>ProjectID</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>ProjectID de Fact_Costos. Presupuesto, comprometido y costo real.</t>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Clave del proyecto minero sintético.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Costo real vs presupuesto, variación de costo, costo por área/equipo/proyecto.</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>ProjectID -&gt; Dim_Proyecto.ProjectID; EquipmentID -&gt; Dim_Equipo.EquipmentID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3104,17 +6087,47 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
+          <t>Presupuesto, comprometido y costo real de operacion, mantenimiento, energia, repuestos, contratistas y proyectos mineros.</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Una fila por registro de costo presupuestado, comprometido y real.</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
           <t>AreaID</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AreaID de Fact_Costos. Presupuesto, comprometido y costo real.</t>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Clave del área minera. En dimensiones es identificador; en hechos es llave foránea hacia Dim_Area.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Costo real vs presupuesto, variación de costo, costo por área/equipo/proyecto.</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>ProjectID -&gt; Dim_Proyecto.ProjectID; EquipmentID -&gt; Dim_Equipo.EquipmentID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3131,17 +6144,47 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
+          <t>Presupuesto, comprometido y costo real de operacion, mantenimiento, energia, repuestos, contratistas y proyectos mineros.</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Una fila por registro de costo presupuestado, comprometido y real.</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
           <t>EquipmentID</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>EquipmentID de Fact_Costos. Presupuesto, comprometido y costo real.</t>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Clave del equipo o activo. En hechos permite conectar costos, mantenimiento, energía e incidentes con Dim_Equipo.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Costo real vs presupuesto, variación de costo, costo por área/equipo/proyecto.</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>ProjectID -&gt; Dim_Proyecto.ProjectID; EquipmentID -&gt; Dim_Equipo.EquipmentID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3158,17 +6201,47 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
+          <t>Presupuesto, comprometido y costo real de operacion, mantenimiento, energia, repuestos, contratistas y proyectos mineros.</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Una fila por registro de costo presupuestado, comprometido y real.</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
           <t>CostCategory</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>CostCategory de Fact_Costos. Presupuesto, comprometido y costo real.</t>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Categoría de costo minero: repuestos, mano de obra, contratistas, energía, neumáticos, componentes mayores, instrumentación, seguridad, automatización, etc.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Neumáticos; Energía; Componentes mayores; Parada planta</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Costo real vs presupuesto, variación de costo, costo por área/equipo/proyecto.</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>ProjectID -&gt; Dim_Proyecto.ProjectID; EquipmentID -&gt; Dim_Equipo.EquipmentID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3185,17 +6258,47 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
+          <t>Presupuesto, comprometido y costo real de operacion, mantenimiento, energia, repuestos, contratistas y proyectos mineros.</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Una fila por registro de costo presupuestado, comprometido y real.</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
           <t>BudgetAmount</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>BudgetAmount de Fact_Costos. Presupuesto, comprometido y costo real.</t>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Monto presupuestado.</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Costo real vs presupuesto, variación de costo, costo por área/equipo/proyecto.</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>ProjectID -&gt; Dim_Proyecto.ProjectID; EquipmentID -&gt; Dim_Equipo.EquipmentID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3212,17 +6315,47 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
+          <t>Presupuesto, comprometido y costo real de operacion, mantenimiento, energia, repuestos, contratistas y proyectos mineros.</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Una fila por registro de costo presupuestado, comprometido y real.</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
           <t>ActualAmount</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>ActualAmount de Fact_Costos. Presupuesto, comprometido y costo real.</t>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Monto real registrado.</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Costo real vs presupuesto, variación de costo, costo por área/equipo/proyecto.</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Revisar outliers antes de concluir causas; algunos patrones son intencionales para el laboratorio.</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>ProjectID -&gt; Dim_Proyecto.ProjectID; EquipmentID -&gt; Dim_Equipo.EquipmentID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3239,17 +6372,47 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
+          <t>Presupuesto, comprometido y costo real de operacion, mantenimiento, energia, repuestos, contratistas y proyectos mineros.</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Una fila por registro de costo presupuestado, comprometido y real.</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
           <t>CommittedAmount</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>CommittedAmount de Fact_Costos. Presupuesto, comprometido y costo real.</t>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Monto comprometido, por ejemplo orden de compra o contrato aún no devengado.</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Costo real vs presupuesto, variación de costo, costo por área/equipo/proyecto.</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>ProjectID -&gt; Dim_Proyecto.ProjectID; EquipmentID -&gt; Dim_Equipo.EquipmentID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3266,17 +6429,47 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
+          <t>Presupuesto, comprometido y costo real de operacion, mantenimiento, energia, repuestos, contratistas y proyectos mineros.</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Una fila por registro de costo presupuestado, comprometido y real.</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
           <t>VendorType</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>VendorType de Fact_Costos. Presupuesto, comprometido y costo real.</t>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Tipo de proveedor o fuente de gasto: interno, contratista, OEM sintético o servicio especializado.</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Costo real vs presupuesto, variación de costo, costo por área/equipo/proyecto.</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>ProjectID -&gt; Dim_Proyecto.ProjectID; EquipmentID -&gt; Dim_Equipo.EquipmentID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3293,17 +6486,47 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
+          <t>Cumplimiento de acuerdos de servicio para servicios operacionales mineros.</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Una fila por compromiso SLA asociado a una orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
           <t>SLAID</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>SLAID de Fact_SLA. Cumplimiento de acuerdos de servicio.</t>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Clave del compromiso SLA.</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>% cumplimiento SLA, breach hours, resolución promedio, SLA por prioridad, servicio y área.</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>WorkOrderID -&gt; Fact_OrdenesTrabajo.WorkOrderID; ClientID -&gt; Dim_Cliente.ClientID; ServiceID -&gt; Dim_Servicio.ServiceID; AreaID -&gt; Dim_Area.AreaID; PriorityID -&gt; Dim_Prioridad.PriorityID; CreatedDateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3320,17 +6543,47 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
+          <t>Cumplimiento de acuerdos de servicio para servicios operacionales mineros.</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Una fila por compromiso SLA asociado a una orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
           <t>WorkOrderID</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>WorkOrderID de Fact_SLA. Cumplimiento de acuerdos de servicio.</t>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Clave de la orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>% cumplimiento SLA, breach hours, resolución promedio, SLA por prioridad, servicio y área.</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>WorkOrderID -&gt; Fact_OrdenesTrabajo.WorkOrderID; ClientID -&gt; Dim_Cliente.ClientID; ServiceID -&gt; Dim_Servicio.ServiceID; AreaID -&gt; Dim_Area.AreaID; PriorityID -&gt; Dim_Prioridad.PriorityID; CreatedDateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3347,17 +6600,47 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
+          <t>Cumplimiento de acuerdos de servicio para servicios operacionales mineros.</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Una fila por compromiso SLA asociado a una orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
           <t>ClientID</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>ClientID de Fact_SLA. Cumplimiento de acuerdos de servicio.</t>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Clave del cliente interno, gerencia o contrato sintético.</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>% cumplimiento SLA, breach hours, resolución promedio, SLA por prioridad, servicio y área.</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>WorkOrderID -&gt; Fact_OrdenesTrabajo.WorkOrderID; ClientID -&gt; Dim_Cliente.ClientID; ServiceID -&gt; Dim_Servicio.ServiceID; AreaID -&gt; Dim_Area.AreaID; PriorityID -&gt; Dim_Prioridad.PriorityID; CreatedDateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3374,17 +6657,47 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
+          <t>Cumplimiento de acuerdos de servicio para servicios operacionales mineros.</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Una fila por compromiso SLA asociado a una orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
           <t>ServiceID</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>ServiceID de Fact_SLA. Cumplimiento de acuerdos de servicio.</t>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Clave del servicio operacional.</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>% cumplimiento SLA, breach hours, resolución promedio, SLA por prioridad, servicio y área.</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>WorkOrderID -&gt; Fact_OrdenesTrabajo.WorkOrderID; ClientID -&gt; Dim_Cliente.ClientID; ServiceID -&gt; Dim_Servicio.ServiceID; AreaID -&gt; Dim_Area.AreaID; PriorityID -&gt; Dim_Prioridad.PriorityID; CreatedDateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3401,17 +6714,47 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
+          <t>Cumplimiento de acuerdos de servicio para servicios operacionales mineros.</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Una fila por compromiso SLA asociado a una orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
           <t>AreaID</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AreaID de Fact_SLA. Cumplimiento de acuerdos de servicio.</t>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Clave del área minera. En dimensiones es identificador; en hechos es llave foránea hacia Dim_Area.</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>% cumplimiento SLA, breach hours, resolución promedio, SLA por prioridad, servicio y área.</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>WorkOrderID -&gt; Fact_OrdenesTrabajo.WorkOrderID; ClientID -&gt; Dim_Cliente.ClientID; ServiceID -&gt; Dim_Servicio.ServiceID; AreaID -&gt; Dim_Area.AreaID; PriorityID -&gt; Dim_Prioridad.PriorityID; CreatedDateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3428,17 +6771,47 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
+          <t>Cumplimiento de acuerdos de servicio para servicios operacionales mineros.</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Una fila por compromiso SLA asociado a una orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
           <t>PriorityID</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>PriorityID de Fact_SLA. Cumplimiento de acuerdos de servicio.</t>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Clave de prioridad operacional.</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>% cumplimiento SLA, breach hours, resolución promedio, SLA por prioridad, servicio y área.</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>WorkOrderID -&gt; Fact_OrdenesTrabajo.WorkOrderID; ClientID -&gt; Dim_Cliente.ClientID; ServiceID -&gt; Dim_Servicio.ServiceID; AreaID -&gt; Dim_Area.AreaID; PriorityID -&gt; Dim_Prioridad.PriorityID; CreatedDateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3455,17 +6828,47 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
+          <t>Cumplimiento de acuerdos de servicio para servicios operacionales mineros.</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Una fila por compromiso SLA asociado a una orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
           <t>CreatedDateKey</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>CreatedDateKey de Fact_SLA. Cumplimiento de acuerdos de servicio.</t>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Fecha de creación de la orden o del compromiso SLA.</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>% cumplimiento SLA, breach hours, resolución promedio, SLA por prioridad, servicio y área.</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>WorkOrderID -&gt; Fact_OrdenesTrabajo.WorkOrderID; ClientID -&gt; Dim_Cliente.ClientID; ServiceID -&gt; Dim_Servicio.ServiceID; AreaID -&gt; Dim_Area.AreaID; PriorityID -&gt; Dim_Prioridad.PriorityID; CreatedDateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3482,17 +6885,47 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
+          <t>Cumplimiento de acuerdos de servicio para servicios operacionales mineros.</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Una fila por compromiso SLA asociado a una orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
           <t>CommittedDateKey</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>CommittedDateKey de Fact_SLA. Cumplimiento de acuerdos de servicio.</t>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Fecha comprometida para resolver o cumplir el servicio.</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>% cumplimiento SLA, breach hours, resolución promedio, SLA por prioridad, servicio y área.</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>WorkOrderID -&gt; Fact_OrdenesTrabajo.WorkOrderID; ClientID -&gt; Dim_Cliente.ClientID; ServiceID -&gt; Dim_Servicio.ServiceID; AreaID -&gt; Dim_Area.AreaID; PriorityID -&gt; Dim_Prioridad.PriorityID; CreatedDateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3509,17 +6942,47 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
+          <t>Cumplimiento de acuerdos de servicio para servicios operacionales mineros.</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Una fila por compromiso SLA asociado a una orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
           <t>ResolvedDateKey</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>ResolvedDateKey de Fact_SLA. Cumplimiento de acuerdos de servicio.</t>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Fecha real de resolución del servicio.</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>% cumplimiento SLA, breach hours, resolución promedio, SLA por prioridad, servicio y área.</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>En raw puede aparecer nulo o con formato inconsistente; en clean debe permitir análisis de cierre/resolución.</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>WorkOrderID -&gt; Fact_OrdenesTrabajo.WorkOrderID; ClientID -&gt; Dim_Cliente.ClientID; ServiceID -&gt; Dim_Servicio.ServiceID; AreaID -&gt; Dim_Area.AreaID; PriorityID -&gt; Dim_Prioridad.PriorityID; CreatedDateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3536,17 +6999,47 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
+          <t>Cumplimiento de acuerdos de servicio para servicios operacionales mineros.</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Una fila por compromiso SLA asociado a una orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
           <t>TargetHours</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>TargetHours de Fact_SLA. Cumplimiento de acuerdos de servicio.</t>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Horas objetivo del SLA.</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>% cumplimiento SLA, breach hours, resolución promedio, SLA por prioridad, servicio y área.</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>WorkOrderID -&gt; Fact_OrdenesTrabajo.WorkOrderID; ClientID -&gt; Dim_Cliente.ClientID; ServiceID -&gt; Dim_Servicio.ServiceID; AreaID -&gt; Dim_Area.AreaID; PriorityID -&gt; Dim_Prioridad.PriorityID; CreatedDateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3563,17 +7056,47 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
+          <t>Cumplimiento de acuerdos de servicio para servicios operacionales mineros.</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Una fila por compromiso SLA asociado a una orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
           <t>ActualHours</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>ActualHours de Fact_SLA. Cumplimiento de acuerdos de servicio.</t>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Horas reales consumidas por la orden o el SLA.</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>% cumplimiento SLA, breach hours, resolución promedio, SLA por prioridad, servicio y área.</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>WorkOrderID -&gt; Fact_OrdenesTrabajo.WorkOrderID; ClientID -&gt; Dim_Cliente.ClientID; ServiceID -&gt; Dim_Servicio.ServiceID; AreaID -&gt; Dim_Area.AreaID; PriorityID -&gt; Dim_Prioridad.PriorityID; CreatedDateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3590,17 +7113,47 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
+          <t>Cumplimiento de acuerdos de servicio para servicios operacionales mineros.</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Una fila por compromiso SLA asociado a una orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
           <t>SLAMetFlag</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>SLAMetFlag de Fact_SLA. Cumplimiento de acuerdos de servicio.</t>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Indica si el SLA fue cumplido.</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>% cumplimiento SLA, breach hours, resolución promedio, SLA por prioridad, servicio y área.</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>WorkOrderID -&gt; Fact_OrdenesTrabajo.WorkOrderID; ClientID -&gt; Dim_Cliente.ClientID; ServiceID -&gt; Dim_Servicio.ServiceID; AreaID -&gt; Dim_Area.AreaID; PriorityID -&gt; Dim_Prioridad.PriorityID; CreatedDateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3617,17 +7170,47 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
+          <t>Cumplimiento de acuerdos de servicio para servicios operacionales mineros.</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Una fila por compromiso SLA asociado a una orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
           <t>BreachHours</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>BreachHours de Fact_SLA. Cumplimiento de acuerdos de servicio.</t>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Horas de incumplimiento. Cero significa SLA cumplido o sin brecha.</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>% cumplimiento SLA, breach hours, resolución promedio, SLA por prioridad, servicio y área.</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>WorkOrderID -&gt; Fact_OrdenesTrabajo.WorkOrderID; ClientID -&gt; Dim_Cliente.ClientID; ServiceID -&gt; Dim_Servicio.ServiceID; AreaID -&gt; Dim_Area.AreaID; PriorityID -&gt; Dim_Prioridad.PriorityID; CreatedDateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3644,17 +7227,47 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
+          <t>Eventos de mantenimiento y confiabilidad minera con downtime, repair hours, modos de falla y costos.</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Una fila por evento de mantenimiento o falla.</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
           <t>MaintenanceID</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="F120" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>MaintenanceID de Fact_Mantenimiento. Eventos de mantenimiento y downtime.</t>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Clave del evento de mantenimiento.</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Downtime, MTTR aproximado, costo de mantenimiento, correctivo vs preventivo y fallas repetitivas.</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; AreaID -&gt; Dim_Area.AreaID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3671,17 +7284,47 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
+          <t>Eventos de mantenimiento y confiabilidad minera con downtime, repair hours, modos de falla y costos.</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Una fila por evento de mantenimiento o falla.</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
           <t>DateKey</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>DateKey de Fact_Mantenimiento. Eventos de mantenimiento y downtime.</t>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Clave de fecha en formato yyyymmdd. Permite relacionar hechos con Dim_Fecha sin depender de formatos regionales.</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Downtime, MTTR aproximado, costo de mantenimiento, correctivo vs preventivo y fallas repetitivas.</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; AreaID -&gt; Dim_Area.AreaID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3698,17 +7341,47 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
+          <t>Eventos de mantenimiento y confiabilidad minera con downtime, repair hours, modos de falla y costos.</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Una fila por evento de mantenimiento o falla.</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
           <t>EquipmentID</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>EquipmentID de Fact_Mantenimiento. Eventos de mantenimiento y downtime.</t>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Clave del equipo o activo. En hechos permite conectar costos, mantenimiento, energía e incidentes con Dim_Equipo.</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Downtime, MTTR aproximado, costo de mantenimiento, correctivo vs preventivo y fallas repetitivas.</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; AreaID -&gt; Dim_Area.AreaID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3725,17 +7398,47 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
+          <t>Eventos de mantenimiento y confiabilidad minera con downtime, repair hours, modos de falla y costos.</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Una fila por evento de mantenimiento o falla.</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
           <t>AreaID</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AreaID de Fact_Mantenimiento. Eventos de mantenimiento y downtime.</t>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Clave del área minera. En dimensiones es identificador; en hechos es llave foránea hacia Dim_Area.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Downtime, MTTR aproximado, costo de mantenimiento, correctivo vs preventivo y fallas repetitivas.</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; AreaID -&gt; Dim_Area.AreaID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3752,17 +7455,47 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
+          <t>Eventos de mantenimiento y confiabilidad minera con downtime, repair hours, modos de falla y costos.</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Una fila por evento de mantenimiento o falla.</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
           <t>WorkTypeID</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>WorkTypeID de Fact_Mantenimiento. Eventos de mantenimiento y downtime.</t>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Clave del tipo de trabajo.</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Downtime, MTTR aproximado, costo de mantenimiento, correctivo vs preventivo y fallas repetitivas.</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; AreaID -&gt; Dim_Area.AreaID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3779,17 +7512,47 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
+          <t>Eventos de mantenimiento y confiabilidad minera con downtime, repair hours, modos de falla y costos.</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Una fila por evento de mantenimiento o falla.</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
           <t>PriorityID</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>PriorityID de Fact_Mantenimiento. Eventos de mantenimiento y downtime.</t>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Clave de prioridad operacional.</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Downtime, MTTR aproximado, costo de mantenimiento, correctivo vs preventivo y fallas repetitivas.</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; AreaID -&gt; Dim_Area.AreaID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3806,17 +7569,47 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
+          <t>Eventos de mantenimiento y confiabilidad minera con downtime, repair hours, modos de falla y costos.</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Una fila por evento de mantenimiento o falla.</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
           <t>FailureMode</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>FailureMode de Fact_Mantenimiento. Eventos de mantenimiento y downtime.</t>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Modo de falla minero, por ejemplo bloqueo de chancador, corte de correa, fuga hidráulica, falla de bomba o pérdida de comunicación PLC.</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Bloqueo de chancador; Corte de correa; Falla de bomba de pulpa</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Downtime, MTTR aproximado, costo de mantenimiento, correctivo vs preventivo y fallas repetitivas.</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; AreaID -&gt; Dim_Area.AreaID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3833,17 +7626,47 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
+          <t>Eventos de mantenimiento y confiabilidad minera con downtime, repair hours, modos de falla y costos.</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Una fila por evento de mantenimiento o falla.</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
           <t>SystemCategory</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>SystemCategory de Fact_Mantenimiento. Eventos de mantenimiento y downtime.</t>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Sistema afectado: Hidráulico, Eléctrico, Mecánico, Neumáticos, Correas, Chancado, Molienda, Bombas, Instrumentación, Control, Energía o Seguridad.</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Chancado; Correas; Molienda; Control</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Downtime, MTTR aproximado, costo de mantenimiento, correctivo vs preventivo y fallas repetitivas.</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; AreaID -&gt; Dim_Area.AreaID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3860,17 +7683,47 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
+          <t>Eventos de mantenimiento y confiabilidad minera con downtime, repair hours, modos de falla y costos.</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Una fila por evento de mantenimiento o falla.</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
           <t>DowntimeHours</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>DowntimeHours de Fact_Mantenimiento. Eventos de mantenimiento y downtime.</t>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Horas de indisponibilidad operacional atribuidas al evento.</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Downtime, MTTR aproximado, costo de mantenimiento, correctivo vs preventivo y fallas repetitivas.</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Revisar outliers antes de concluir causas; algunos patrones son intencionales para el laboratorio.</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; AreaID -&gt; Dim_Area.AreaID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3887,17 +7740,47 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
+          <t>Eventos de mantenimiento y confiabilidad minera con downtime, repair hours, modos de falla y costos.</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Una fila por evento de mantenimiento o falla.</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
           <t>RepairHours</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>RepairHours de Fact_Mantenimiento. Eventos de mantenimiento y downtime.</t>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Horas invertidas en reparación. No siempre equivalen al downtime porque puede haber espera, permisos o pruebas.</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Downtime, MTTR aproximado, costo de mantenimiento, correctivo vs preventivo y fallas repetitivas.</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; AreaID -&gt; Dim_Area.AreaID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3914,17 +7797,47 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
+          <t>Eventos de mantenimiento y confiabilidad minera con downtime, repair hours, modos de falla y costos.</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Una fila por evento de mantenimiento o falla.</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
           <t>MaintenanceCost</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>MaintenanceCost de Fact_Mantenimiento. Eventos de mantenimiento y downtime.</t>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Costo del evento de mantenimiento.</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Downtime, MTTR aproximado, costo de mantenimiento, correctivo vs preventivo y fallas repetitivas.</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Revisar outliers antes de concluir causas; algunos patrones son intencionales para el laboratorio.</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; AreaID -&gt; Dim_Area.AreaID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3941,17 +7854,47 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
+          <t>Eventos de mantenimiento y confiabilidad minera con downtime, repair hours, modos de falla y costos.</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Una fila por evento de mantenimiento o falla.</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
           <t>PlannedFlag</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>PlannedFlag de Fact_Mantenimiento. Eventos de mantenimiento y downtime.</t>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Indica si el registro corresponde a trabajo planificado. En mantenimiento ayuda a separar preventivo/planificado de correctivo no planificado.</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Downtime, MTTR aproximado, costo de mantenimiento, correctivo vs preventivo y fallas repetitivas.</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>EquipmentID -&gt; Dim_Equipo.EquipmentID; AreaID -&gt; Dim_Area.AreaID; WorkTypeID -&gt; Dim_TipoTrabajo.WorkTypeID; PriorityID -&gt; Dim_Prioridad.PriorityID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3968,17 +7911,47 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
+          <t>Incidentes HSE y acciones correctivas en contexto minero sintetico.</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Una fila por incidente HSE o acción correctiva.</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
           <t>IncidentID</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>IncidentID de Fact_Incidentes. Incidentes de seguridad y acciones correctivas.</t>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Clave del incidente o acción HSE.</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Incidentes por severidad, acciones abiertas/vencidas, días abiertos y foco HSE por área.</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; EquipmentID -&gt; Dim_Equipo.EquipmentID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -3995,17 +7968,47 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
+          <t>Incidentes HSE y acciones correctivas en contexto minero sintetico.</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Una fila por incidente HSE o acción correctiva.</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
           <t>DateKey</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>DateKey de Fact_Incidentes. Incidentes de seguridad y acciones correctivas.</t>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Clave de fecha en formato yyyymmdd. Permite relacionar hechos con Dim_Fecha sin depender de formatos regionales.</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Incidentes por severidad, acciones abiertas/vencidas, días abiertos y foco HSE por área.</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; EquipmentID -&gt; Dim_Equipo.EquipmentID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4022,17 +8025,47 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
+          <t>Incidentes HSE y acciones correctivas en contexto minero sintetico.</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Una fila por incidente HSE o acción correctiva.</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
           <t>AreaID</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AreaID de Fact_Incidentes. Incidentes de seguridad y acciones correctivas.</t>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Clave del área minera. En dimensiones es identificador; en hechos es llave foránea hacia Dim_Area.</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Incidentes por severidad, acciones abiertas/vencidas, días abiertos y foco HSE por área.</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; EquipmentID -&gt; Dim_Equipo.EquipmentID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4049,17 +8082,47 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
+          <t>Incidentes HSE y acciones correctivas en contexto minero sintetico.</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Una fila por incidente HSE o acción correctiva.</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
           <t>EquipmentID</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>EquipmentID de Fact_Incidentes. Incidentes de seguridad y acciones correctivas.</t>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Clave del equipo o activo. En hechos permite conectar costos, mantenimiento, energía e incidentes con Dim_Equipo.</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Incidentes por severidad, acciones abiertas/vencidas, días abiertos y foco HSE por área.</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; EquipmentID -&gt; Dim_Equipo.EquipmentID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4076,17 +8139,47 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
+          <t>Incidentes HSE y acciones correctivas en contexto minero sintetico.</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Una fila por incidente HSE o acción correctiva.</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
           <t>LocationID</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>LocationID de Fact_Incidentes. Incidentes de seguridad y acciones correctivas.</t>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Clave de ubicación. En dimensiones es identificador; en hechos permite analizar por lugar físico de faena.</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Incidentes por severidad, acciones abiertas/vencidas, días abiertos y foco HSE por área.</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; EquipmentID -&gt; Dim_Equipo.EquipmentID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4103,17 +8196,47 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
+          <t>Incidentes HSE y acciones correctivas en contexto minero sintetico.</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Una fila por incidente HSE o acción correctiva.</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Severity de Fact_Incidentes. Incidentes de seguridad y acciones correctivas.</t>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Severidad del incidente: Baja, Media, Alta o Crítica.</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Incidentes por severidad, acciones abiertas/vencidas, días abiertos y foco HSE por área.</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; EquipmentID -&gt; Dim_Equipo.EquipmentID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4130,17 +8253,47 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
+          <t>Incidentes HSE y acciones correctivas en contexto minero sintetico.</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Una fila por incidente HSE o acción correctiva.</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
           <t>IncidentType</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>IncidentType de Fact_Incidentes. Incidentes de seguridad y acciones correctivas.</t>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Tipo de incidente HSE u operacional.</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Casi accidente; Evento HSE; Riesgo geotécnico; Falla de control crítico</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Incidentes por severidad, acciones abiertas/vencidas, días abiertos y foco HSE por área.</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; EquipmentID -&gt; Dim_Equipo.EquipmentID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4157,17 +8310,47 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
+          <t>Incidentes HSE y acciones correctivas en contexto minero sintetico.</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Una fila por incidente HSE o acción correctiva.</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
           <t>CorrectiveActionStatus</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>CorrectiveActionStatus de Fact_Incidentes. Incidentes de seguridad y acciones correctivas.</t>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Estado de la acción correctiva asociada al incidente.</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Incidentes por severidad, acciones abiertas/vencidas, días abiertos y foco HSE por área.</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; EquipmentID -&gt; Dim_Equipo.EquipmentID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4184,17 +8367,47 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
+          <t>Incidentes HSE y acciones correctivas en contexto minero sintetico.</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Una fila por incidente HSE o acción correctiva.</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
           <t>DaysOpen</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>DaysOpen de Fact_Incidentes. Incidentes de seguridad y acciones correctivas.</t>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Días que la acción correctiva lleva abierta. Cero cuando ya está cerrada.</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Incidentes por severidad, acciones abiertas/vencidas, días abiertos y foco HSE por área.</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; EquipmentID -&gt; Dim_Equipo.EquipmentID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4211,17 +8424,47 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
+          <t>Incidentes HSE y acciones correctivas en contexto minero sintetico.</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Una fila por incidente HSE o acción correctiva.</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
           <t>LostTimeFlag</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>LostTimeFlag de Fact_Incidentes. Incidentes de seguridad y acciones correctivas.</t>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Indica si el incidente generó tiempo perdido.</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Incidentes por severidad, acciones abiertas/vencidas, días abiertos y foco HSE por área.</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; EquipmentID -&gt; Dim_Equipo.EquipmentID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4238,17 +8481,47 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
+          <t>Incidentes HSE y acciones correctivas en contexto minero sintetico.</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Una fila por incidente HSE o acción correctiva.</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
           <t>RiskCategory</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>RiskCategory de Fact_Incidentes. Incidentes de seguridad y acciones correctivas.</t>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Categoría de riesgo: Seguridad, Operación, Ambiente, Calidad o Geotecnia.</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Incidentes por severidad, acciones abiertas/vencidas, días abiertos y foco HSE por área.</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; EquipmentID -&gt; Dim_Equipo.EquipmentID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4265,17 +8538,47 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
+          <t>Consumo energetico, costo y output operacional asociado a equipos y areas mineras.</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Una fila por medición de consumo energético por equipo, área, ubicación y turno.</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
           <t>EnergyID</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="F143" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>EnergyID de Fact_Energia. Consumo energético, costo y producción asociada.</t>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Clave del registro energético.</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>kWh total, costo energía, kWh por tonelada, consumo anormal por área/equipo/turno.</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; EquipmentID -&gt; Dim_Equipo.EquipmentID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4292,17 +8595,47 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
+          <t>Consumo energetico, costo y output operacional asociado a equipos y areas mineras.</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Una fila por medición de consumo energético por equipo, área, ubicación y turno.</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
           <t>DateKey</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>DateKey de Fact_Energia. Consumo energético, costo y producción asociada.</t>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Clave de fecha en formato yyyymmdd. Permite relacionar hechos con Dim_Fecha sin depender de formatos regionales.</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>kWh total, costo energía, kWh por tonelada, consumo anormal por área/equipo/turno.</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; EquipmentID -&gt; Dim_Equipo.EquipmentID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4319,17 +8652,47 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
+          <t>Consumo energetico, costo y output operacional asociado a equipos y areas mineras.</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Una fila por medición de consumo energético por equipo, área, ubicación y turno.</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
           <t>AreaID</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AreaID de Fact_Energia. Consumo energético, costo y producción asociada.</t>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Clave del área minera. En dimensiones es identificador; en hechos es llave foránea hacia Dim_Area.</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>kWh total, costo energía, kWh por tonelada, consumo anormal por área/equipo/turno.</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; EquipmentID -&gt; Dim_Equipo.EquipmentID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4346,17 +8709,47 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
+          <t>Consumo energetico, costo y output operacional asociado a equipos y areas mineras.</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Una fila por medición de consumo energético por equipo, área, ubicación y turno.</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
           <t>EquipmentID</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>EquipmentID de Fact_Energia. Consumo energético, costo y producción asociada.</t>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Clave del equipo o activo. En hechos permite conectar costos, mantenimiento, energía e incidentes con Dim_Equipo.</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>kWh total, costo energía, kWh por tonelada, consumo anormal por área/equipo/turno.</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; EquipmentID -&gt; Dim_Equipo.EquipmentID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4373,17 +8766,47 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
+          <t>Consumo energetico, costo y output operacional asociado a equipos y areas mineras.</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Una fila por medición de consumo energético por equipo, área, ubicación y turno.</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
           <t>LocationID</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>LocationID de Fact_Energia. Consumo energético, costo y producción asociada.</t>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Clave de ubicación. En dimensiones es identificador; en hechos permite analizar por lugar físico de faena.</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>kWh total, costo energía, kWh por tonelada, consumo anormal por área/equipo/turno.</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; EquipmentID -&gt; Dim_Equipo.EquipmentID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4400,17 +8823,47 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
+          <t>Consumo energetico, costo y output operacional asociado a equipos y areas mineras.</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Una fila por medición de consumo energético por equipo, área, ubicación y turno.</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
           <t>kWh</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>kWh de Fact_Energia. Consumo energético, costo y producción asociada.</t>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Consumo energético registrado en kilowatt-hora.</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>kWh total, costo energía, kWh por tonelada, consumo anormal por área/equipo/turno.</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Revisar outliers antes de concluir causas; algunos patrones son intencionales para el laboratorio.</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; EquipmentID -&gt; Dim_Equipo.EquipmentID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4427,17 +8880,47 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
+          <t>Consumo energetico, costo y output operacional asociado a equipos y areas mineras.</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Una fila por medición de consumo energético por equipo, área, ubicación y turno.</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
           <t>EnergyCost</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>EnergyCost de Fact_Energia. Consumo energético, costo y producción asociada.</t>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Costo energético asociado al consumo.</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>kWh total, costo energía, kWh por tonelada, consumo anormal por área/equipo/turno.</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; EquipmentID -&gt; Dim_Equipo.EquipmentID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4454,17 +8937,47 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
+          <t>Consumo energetico, costo y output operacional asociado a equipos y areas mineras.</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Una fila por medición de consumo energético por equipo, área, ubicación y turno.</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
           <t>OperatingHours</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>OperatingHours de Fact_Energia. Consumo energético, costo y producción asociada.</t>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Horas de operación del equipo o sistema en el registro.</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>kWh total, costo energía, kWh por tonelada, consumo anormal por área/equipo/turno.</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; EquipmentID -&gt; Dim_Equipo.EquipmentID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4481,17 +8994,47 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
+          <t>Consumo energetico, costo y output operacional asociado a equipos y areas mineras.</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Una fila por medición de consumo energético por equipo, área, ubicación y turno.</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
           <t>OutputUnits</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>OutputUnits de Fact_Energia. Consumo energético, costo y producción asociada.</t>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Output operacional asociado al consumo. En mina/planta se interpreta como toneladas aproximadas u otra unidad operativa sintética.</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>kWh total, costo energía, kWh por tonelada, consumo anormal por área/equipo/turno.</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; EquipmentID -&gt; Dim_Equipo.EquipmentID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4508,17 +9051,47 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
+          <t>Consumo energetico, costo y output operacional asociado a equipos y areas mineras.</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Una fila por medición de consumo energético por equipo, área, ubicación y turno.</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
           <t>Shift</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Shift de Fact_Energia. Consumo energético, costo y producción asociada.</t>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Turno operacional: Día, Tarde o Noche.</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Día; Tarde; Noche</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>kWh total, costo energía, kWh por tonelada, consumo anormal por área/equipo/turno.</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; EquipmentID -&gt; Dim_Equipo.EquipmentID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4535,17 +9108,47 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
+          <t>Produccion u output operacional por turno, area, responsable y ubicacion.</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Una fila por medición de output operacional por turno.</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
           <t>ProductivityID</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
+      <c r="F153" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>ProductivityID de Fact_Productividad. Producción, horas laborales y productividad.</t>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Clave del registro de productividad.</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Cumplimiento de producción, productividad por turno, toneladas por hora productiva y brecha plan vs real.</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4562,17 +9165,47 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
+          <t>Produccion u output operacional por turno, area, responsable y ubicacion.</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Una fila por medición de output operacional por turno.</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
           <t>DateKey</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>DateKey de Fact_Productividad. Producción, horas laborales y productividad.</t>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Clave de fecha en formato yyyymmdd. Permite relacionar hechos con Dim_Fecha sin depender de formatos regionales.</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Cumplimiento de producción, productividad por turno, toneladas por hora productiva y brecha plan vs real.</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4589,17 +9222,47 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
+          <t>Produccion u output operacional por turno, area, responsable y ubicacion.</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Una fila por medición de output operacional por turno.</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
           <t>AreaID</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AreaID de Fact_Productividad. Producción, horas laborales y productividad.</t>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Clave del área minera. En dimensiones es identificador; en hechos es llave foránea hacia Dim_Area.</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Cumplimiento de producción, productividad por turno, toneladas por hora productiva y brecha plan vs real.</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4616,17 +9279,47 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
+          <t>Produccion u output operacional por turno, area, responsable y ubicacion.</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Una fila por medición de output operacional por turno.</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
           <t>ResponsibleID</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>ResponsibleID de Fact_Productividad. Producción, horas laborales y productividad.</t>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Clave del responsable o rol asignado.</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Cumplimiento de producción, productividad por turno, toneladas por hora productiva y brecha plan vs real.</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4643,17 +9336,47 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
+          <t>Produccion u output operacional por turno, area, responsable y ubicacion.</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Una fila por medición de output operacional por turno.</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
           <t>LocationID</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>FK/atributo</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>LocationID de Fact_Productividad. Producción, horas laborales y productividad.</t>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Clave de ubicación. En dimensiones es identificador; en hechos permite analizar por lugar físico de faena.</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Cumplimiento de producción, productividad por turno, toneladas por hora productiva y brecha plan vs real.</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4670,17 +9393,47 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
+          <t>Produccion u output operacional por turno, area, responsable y ubicacion.</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Una fila por medición de output operacional por turno.</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
           <t>Shift</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Shift de Fact_Productividad. Producción, horas laborales y productividad.</t>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Turno operacional: Día, Tarde o Noche.</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Día; Tarde; Noche</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Cumplimiento de producción, productividad por turno, toneladas por hora productiva y brecha plan vs real.</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4697,17 +9450,47 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
+          <t>Produccion u output operacional por turno, area, responsable y ubicacion.</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Una fila por medición de output operacional por turno.</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
           <t>PlannedOutput</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>PlannedOutput de Fact_Productividad. Producción, horas laborales y productividad.</t>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Output planificado por turno o área. En mina puede representar toneladas movidas; en planta, toneladas chancadas o procesadas.</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Cumplimiento de producción, productividad por turno, toneladas por hora productiva y brecha plan vs real.</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4724,17 +9507,47 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
+          <t>Produccion u output operacional por turno, area, responsable y ubicacion.</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Una fila por medición de output operacional por turno.</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
           <t>ActualOutput</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>ActualOutput de Fact_Productividad. Producción, horas laborales y productividad.</t>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Output real observado. Se compara con PlannedOutput para medir cumplimiento operacional.</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Cumplimiento de producción, productividad por turno, toneladas por hora productiva y brecha plan vs real.</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Revisar outliers antes de concluir causas; algunos patrones son intencionales para el laboratorio.</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4751,17 +9564,47 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
+          <t>Produccion u output operacional por turno, area, responsable y ubicacion.</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Una fila por medición de output operacional por turno.</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
           <t>LaborHours</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>LaborHours de Fact_Productividad. Producción, horas laborales y productividad.</t>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Horas laborales disponibles.</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Cumplimiento de producción, productividad por turno, toneladas por hora productiva y brecha plan vs real.</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4778,17 +9621,47 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
+          <t>Produccion u output operacional por turno, area, responsable y ubicacion.</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Una fila por medición de output operacional por turno.</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
           <t>ProductiveHours</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>ProductiveHours de Fact_Productividad. Producción, horas laborales y productividad.</t>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Horas efectivamente productivas.</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Cumplimiento de producción, productividad por turno, toneladas por hora productiva y brecha plan vs real.</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4805,17 +9678,47 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
+          <t>Produccion u output operacional por turno, area, responsable y ubicacion.</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Una fila por medición de output operacional por turno.</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
           <t>NonProductiveHours</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>Métrica/atributo</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>NonProductiveHours de Fact_Productividad. Producción, horas laborales y productividad.</t>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Horas no productivas por espera, fallas, coordinación, permisos, detenciones u otras causas sintéticas.</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Depende del registro.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Cumplimiento de producción, productividad por turno, toneladas por hora productiva y brecha plan vs real.</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Validar contra dimensiones, fechas y reglas de negocio antes de usar en decisiones.</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>AreaID -&gt; Dim_Area.AreaID; ResponsibleID -&gt; Dim_Responsable.ResponsibleID; LocationID -&gt; Dim_Ubicacion.LocationID; DateKey -&gt; Dim_Fecha.DateKey</t>
         </is>
       </c>
     </row>
@@ -4834,7 +9737,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>DimensionTables</t>
         </is>
@@ -4932,7 +9835,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>FactTables</t>
         </is>
@@ -4991,6 +9894,260 @@
       <c r="A9" t="inlineStr">
         <is>
           <t>Fact_Productividad</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TableName</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Dim_Fecha</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Una fila por día calendario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dim_Area</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Una fila por área o proceso minero sintético.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Dim_Equipo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Una fila por activo físico, equipo minero, equipo de planta o sistema OT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Dim_Cliente</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Una fila por cliente interno, gerencia, superintendencia o contrato sintético.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Dim_Proyecto</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Una fila por proyecto minero o iniciativa Tech&amp;Eng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Dim_Responsable</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Una fila por responsable o rol sintético.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Dim_TipoTrabajo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Una fila por tipo de trabajo operacional o de mantenimiento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Dim_Prioridad</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Una fila por nivel de prioridad operacional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Dim_Estado</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Una fila por estado estandarizado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Dim_Servicio</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Una fila por servicio operacional sujeto a SLA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Dim_Ubicacion</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Una fila por ubicación física sintética de faena.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Fact_Proyectos</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Una fila por corte de seguimiento de proyecto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fact_OrdenesTrabajo</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Una fila por orden de trabajo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fact_Costos</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Una fila por registro de costo presupuestado, comprometido y real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fact_SLA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Una fila por compromiso SLA asociado a una orden de trabajo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Fact_Mantenimiento</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Una fila por evento de mantenimiento o falla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Fact_Incidentes</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Una fila por incidente HSE o acción correctiva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fact_Energia</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Una fila por medición de consumo energético por equipo, área, ubicación y turno.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fact_Productividad</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Una fila por medición de output operacional por turno.</t>
         </is>
       </c>
     </row>

--- a/data/project/dictionary/data_dictionary.xlsx
+++ b/data/project/dictionary/data_dictionary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dictionary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dimensions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facts" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grain" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Dictionary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dimensions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Facts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Grain" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
